--- a/docs/Classeur1.xlsx
+++ b/docs/Classeur1.xlsx
@@ -8,17 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/artmskfr/Desktop/Formations/3 - GitHub/Projects/2_HealthScope Diabetes/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F00AF581-4330-B74E-A940-96D9BD96643D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{024BB04C-03A5-0544-B4F4-F15C0C04E80A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9760" yWindow="500" windowWidth="34560" windowHeight="20200" activeTab="2" xr2:uid="{36851BB7-FC07-E946-9954-8F3EFDC14535}"/>
+    <workbookView minimized="1" xWindow="55080" yWindow="-240" windowWidth="29220" windowHeight="20080" activeTab="2" xr2:uid="{36851BB7-FC07-E946-9954-8F3EFDC14535}"/>
   </bookViews>
   <sheets>
     <sheet name="First ver" sheetId="1" r:id="rId1"/>
     <sheet name="Second ver" sheetId="3" r:id="rId2"/>
     <sheet name="Third ver" sheetId="4" r:id="rId3"/>
-    <sheet name="Feuil2" sheetId="2" r:id="rId4"/>
+    <sheet name="Alcohol Use" sheetId="2" r:id="rId4"/>
+    <sheet name="Feuil1" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="856" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="312">
   <si>
     <t xml:space="preserve">Examination Data </t>
   </si>
@@ -1269,12 +1270,87 @@
   <si>
     <t>Ever told you had high blood pressure</t>
   </si>
+  <si>
+    <t>Minutes sedentary activity</t>
+  </si>
+  <si>
+    <t>How often feel overly sleepy during day?</t>
+  </si>
+  <si>
+    <t>Ever told you have prediabetes</t>
+  </si>
+  <si>
+    <t>ALQ120Q</t>
+  </si>
+  <si>
+    <t>ALQ141Q</t>
+  </si>
+  <si>
+    <t>ALQ151</t>
+  </si>
+  <si>
+    <t>Had at least 12 alcohol drinks/lifetime ?</t>
+  </si>
+  <si>
+    <t>How often drink alcohol over 12 mois</t>
+  </si>
+  <si>
+    <t>How days have 4/5 drinks past 12 mois</t>
+  </si>
+  <si>
+    <t>2017-2021</t>
+  </si>
+  <si>
+    <t>2013-2014</t>
+  </si>
+  <si>
+    <t>SLD010H</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> How much sleep do you get (hours)?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLD012 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLQ120 </t>
+  </si>
+  <si>
+    <t>2009-2010</t>
+  </si>
+  <si>
+    <t>ALQ141Q = ALQ140Q</t>
+  </si>
+  <si>
+    <t>2011-2017</t>
+  </si>
+  <si>
+    <t>2017-2020</t>
+  </si>
+  <si>
+    <t>ALQ110 -&gt;</t>
+  </si>
+  <si>
+    <t>ALQ110  -&gt;</t>
+  </si>
+  <si>
+    <t>ALQ120Q -&gt;</t>
+  </si>
+  <si>
+    <t>ALQ141Q -&gt;</t>
+  </si>
+  <si>
+    <t>ALQ150 -&gt;</t>
+  </si>
+  <si>
+    <t>ALQ140Q -&gt;</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16">
+  <fonts count="18">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1379,8 +1455,21 @@
       <color theme="1"/>
       <name val="Aptos Narrow (Corps)"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="0" tint="-0.34998626667073579"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1426,6 +1515,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1537,7 +1632,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="112">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1655,144 +1750,184 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2141,13 +2276,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="27">
-      <c r="C1" s="49" t="s">
+      <c r="C1" s="73" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="73"/>
     </row>
     <row r="2" spans="1:7" ht="19">
       <c r="A2" t="s">
@@ -2156,12 +2291,12 @@
       <c r="B2" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="C2" s="47" t="s">
+      <c r="C2" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="72"/>
     </row>
     <row r="3" spans="1:7">
       <c r="B3" s="11">
@@ -2291,16 +2426,16 @@
       <c r="F10" s="9"/>
     </row>
     <row r="11" spans="1:7" ht="19">
-      <c r="B11" s="47" t="s">
+      <c r="B11" s="72" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="47"/>
-      <c r="D11" s="47"/>
-      <c r="E11" s="47"/>
-      <c r="F11" s="47"/>
+      <c r="C11" s="72"/>
+      <c r="D11" s="72"/>
+      <c r="E11" s="72"/>
+      <c r="F11" s="72"/>
     </row>
     <row r="12" spans="1:7" ht="19">
-      <c r="A12" s="45" t="s">
+      <c r="A12" s="77" t="s">
         <v>234</v>
       </c>
       <c r="B12" s="24">
@@ -2316,7 +2451,7 @@
       <c r="F12" s="26"/>
     </row>
     <row r="13" spans="1:7" ht="34" customHeight="1">
-      <c r="A13" s="45"/>
+      <c r="A13" s="77"/>
       <c r="B13" s="27">
         <v>2</v>
       </c>
@@ -2330,12 +2465,12 @@
       <c r="F13" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="G13" s="51" t="s">
+      <c r="G13" s="74" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="34">
-      <c r="A14" s="45"/>
+      <c r="A14" s="77"/>
       <c r="B14" s="27">
         <v>3</v>
       </c>
@@ -2349,10 +2484,10 @@
       <c r="F14" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="G14" s="52"/>
+      <c r="G14" s="75"/>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="45"/>
+      <c r="A15" s="77"/>
       <c r="B15" s="27">
         <v>4</v>
       </c>
@@ -2368,7 +2503,7 @@
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="45"/>
+      <c r="A16" s="77"/>
       <c r="B16" s="27">
         <v>5</v>
       </c>
@@ -2382,14 +2517,14 @@
       <c r="F16" s="25"/>
     </row>
     <row r="17" spans="1:7" ht="27">
-      <c r="B17" s="49" t="s">
+      <c r="B17" s="73" t="s">
         <v>39</v>
       </c>
-      <c r="C17" s="49"/>
-      <c r="D17" s="49"/>
-      <c r="E17" s="49"/>
-      <c r="F17" s="49"/>
-      <c r="G17" s="49"/>
+      <c r="C17" s="73"/>
+      <c r="D17" s="73"/>
+      <c r="E17" s="73"/>
+      <c r="F17" s="73"/>
+      <c r="G17" s="73"/>
     </row>
     <row r="18" spans="1:7" ht="27">
       <c r="B18" s="22"/>
@@ -2540,23 +2675,23 @@
       <c r="F28" s="9"/>
     </row>
     <row r="29" spans="1:7" ht="27">
-      <c r="B29" s="49" t="s">
+      <c r="B29" s="73" t="s">
         <v>60</v>
       </c>
-      <c r="C29" s="49"/>
-      <c r="D29" s="49"/>
-      <c r="E29" s="49"/>
-      <c r="F29" s="49"/>
-      <c r="G29" s="49"/>
+      <c r="C29" s="73"/>
+      <c r="D29" s="73"/>
+      <c r="E29" s="73"/>
+      <c r="F29" s="73"/>
+      <c r="G29" s="73"/>
     </row>
     <row r="30" spans="1:7" ht="19">
-      <c r="B30" s="47" t="s">
+      <c r="B30" s="72" t="s">
         <v>61</v>
       </c>
-      <c r="C30" s="47"/>
-      <c r="D30" s="47"/>
-      <c r="E30" s="47"/>
-      <c r="F30" s="47"/>
+      <c r="C30" s="72"/>
+      <c r="D30" s="72"/>
+      <c r="E30" s="72"/>
+      <c r="F30" s="72"/>
     </row>
     <row r="31" spans="1:7" ht="19">
       <c r="B31" s="24">
@@ -2601,13 +2736,13 @@
       </c>
     </row>
     <row r="34" spans="2:7" ht="19">
-      <c r="B34" s="47" t="s">
+      <c r="B34" s="72" t="s">
         <v>67</v>
       </c>
-      <c r="C34" s="47"/>
-      <c r="D34" s="47"/>
-      <c r="E34" s="47"/>
-      <c r="F34" s="47"/>
+      <c r="C34" s="72"/>
+      <c r="D34" s="72"/>
+      <c r="E34" s="72"/>
+      <c r="F34" s="72"/>
     </row>
     <row r="35" spans="2:7">
       <c r="B35" s="11">
@@ -2636,13 +2771,13 @@
       <c r="F36" s="9"/>
     </row>
     <row r="37" spans="2:7" ht="19">
-      <c r="B37" s="47" t="s">
+      <c r="B37" s="72" t="s">
         <v>71</v>
       </c>
-      <c r="C37" s="47"/>
-      <c r="D37" s="47"/>
-      <c r="E37" s="47"/>
-      <c r="F37" s="47"/>
+      <c r="C37" s="72"/>
+      <c r="D37" s="72"/>
+      <c r="E37" s="72"/>
+      <c r="F37" s="72"/>
     </row>
     <row r="38" spans="2:7">
       <c r="B38" s="34">
@@ -2697,13 +2832,13 @@
       <c r="F41" s="35"/>
     </row>
     <row r="42" spans="2:7" ht="19">
-      <c r="B42" s="50" t="s">
+      <c r="B42" s="71" t="s">
         <v>88</v>
       </c>
-      <c r="C42" s="50"/>
-      <c r="D42" s="50"/>
-      <c r="E42" s="50"/>
-      <c r="F42" s="50"/>
+      <c r="C42" s="71"/>
+      <c r="D42" s="71"/>
+      <c r="E42" s="71"/>
+      <c r="F42" s="71"/>
     </row>
     <row r="43" spans="2:7">
       <c r="B43" s="11"/>
@@ -2817,7 +2952,7 @@
       </c>
     </row>
     <row r="52" spans="1:7">
-      <c r="A52" s="46" t="s">
+      <c r="A52" s="78" t="s">
         <v>235</v>
       </c>
       <c r="B52" s="11"/>
@@ -2834,7 +2969,7 @@
       </c>
     </row>
     <row r="53" spans="1:7">
-      <c r="A53" s="46"/>
+      <c r="A53" s="78"/>
       <c r="B53" s="11"/>
       <c r="C53" s="9" t="s">
         <v>101</v>
@@ -2849,13 +2984,13 @@
       </c>
     </row>
     <row r="54" spans="1:7" ht="19">
-      <c r="B54" s="47" t="s">
+      <c r="B54" s="72" t="s">
         <v>104</v>
       </c>
-      <c r="C54" s="47"/>
-      <c r="D54" s="47"/>
-      <c r="E54" s="47"/>
-      <c r="F54" s="47"/>
+      <c r="C54" s="72"/>
+      <c r="D54" s="72"/>
+      <c r="E54" s="72"/>
+      <c r="F54" s="72"/>
     </row>
     <row r="55" spans="1:7">
       <c r="C55" t="s">
@@ -2877,13 +3012,13 @@
       </c>
     </row>
     <row r="57" spans="1:7" ht="19">
-      <c r="B57" s="47" t="s">
+      <c r="B57" s="72" t="s">
         <v>108</v>
       </c>
-      <c r="C57" s="47"/>
-      <c r="D57" s="47"/>
-      <c r="E57" s="47"/>
-      <c r="F57" s="47"/>
+      <c r="C57" s="72"/>
+      <c r="D57" s="72"/>
+      <c r="E57" s="72"/>
+      <c r="F57" s="72"/>
     </row>
     <row r="58" spans="1:7">
       <c r="C58" t="s">
@@ -2913,23 +3048,23 @@
       </c>
     </row>
     <row r="61" spans="1:7" ht="27">
-      <c r="B61" s="49" t="s">
+      <c r="B61" s="73" t="s">
         <v>114</v>
       </c>
-      <c r="C61" s="49"/>
-      <c r="D61" s="49"/>
-      <c r="E61" s="49"/>
-      <c r="F61" s="49"/>
-      <c r="G61" s="49"/>
+      <c r="C61" s="73"/>
+      <c r="D61" s="73"/>
+      <c r="E61" s="73"/>
+      <c r="F61" s="73"/>
+      <c r="G61" s="73"/>
     </row>
     <row r="62" spans="1:7" ht="19">
-      <c r="B62" s="47" t="s">
+      <c r="B62" s="72" t="s">
         <v>115</v>
       </c>
-      <c r="C62" s="47"/>
-      <c r="D62" s="47"/>
-      <c r="E62" s="47"/>
-      <c r="F62" s="47"/>
+      <c r="C62" s="72"/>
+      <c r="D62" s="72"/>
+      <c r="E62" s="72"/>
+      <c r="F62" s="72"/>
     </row>
     <row r="63" spans="1:7">
       <c r="C63" t="s">
@@ -3001,13 +3136,13 @@
       </c>
     </row>
     <row r="69" spans="1:6" ht="19">
-      <c r="B69" s="47" t="s">
+      <c r="B69" s="72" t="s">
         <v>128</v>
       </c>
-      <c r="C69" s="47"/>
-      <c r="D69" s="47"/>
-      <c r="E69" s="47"/>
-      <c r="F69" s="47"/>
+      <c r="C69" s="72"/>
+      <c r="D69" s="72"/>
+      <c r="E69" s="72"/>
+      <c r="F69" s="72"/>
     </row>
     <row r="70" spans="1:6">
       <c r="C70" t="s">
@@ -3076,13 +3211,13 @@
       </c>
     </row>
     <row r="76" spans="1:6" ht="19">
-      <c r="B76" s="47" t="s">
+      <c r="B76" s="72" t="s">
         <v>142</v>
       </c>
-      <c r="C76" s="47"/>
-      <c r="D76" s="47"/>
-      <c r="E76" s="47"/>
-      <c r="F76" s="47"/>
+      <c r="C76" s="72"/>
+      <c r="D76" s="72"/>
+      <c r="E76" s="72"/>
+      <c r="F76" s="72"/>
     </row>
     <row r="77" spans="1:6">
       <c r="C77" t="s">
@@ -3112,13 +3247,13 @@
       </c>
     </row>
     <row r="80" spans="1:6" ht="19">
-      <c r="B80" s="47" t="s">
+      <c r="B80" s="72" t="s">
         <v>147</v>
       </c>
-      <c r="C80" s="47"/>
-      <c r="D80" s="47"/>
-      <c r="E80" s="47"/>
-      <c r="F80" s="47"/>
+      <c r="C80" s="72"/>
+      <c r="D80" s="72"/>
+      <c r="E80" s="72"/>
+      <c r="F80" s="72"/>
     </row>
     <row r="81" spans="2:7">
       <c r="C81" t="s">
@@ -3129,7 +3264,7 @@
       </c>
     </row>
     <row r="82" spans="2:7">
-      <c r="B82" s="48" t="s">
+      <c r="B82" s="76" t="s">
         <v>232</v>
       </c>
       <c r="C82" t="s">
@@ -3146,7 +3281,7 @@
       </c>
     </row>
     <row r="83" spans="2:7">
-      <c r="B83" s="48"/>
+      <c r="B83" s="76"/>
       <c r="C83" t="s">
         <v>152</v>
       </c>
@@ -3155,7 +3290,7 @@
       </c>
     </row>
     <row r="84" spans="2:7">
-      <c r="B84" s="48"/>
+      <c r="B84" s="76"/>
       <c r="C84" t="s">
         <v>154</v>
       </c>
@@ -3164,7 +3299,7 @@
       </c>
     </row>
     <row r="85" spans="2:7">
-      <c r="B85" s="48"/>
+      <c r="B85" s="76"/>
       <c r="C85" t="s">
         <v>156</v>
       </c>
@@ -3173,7 +3308,7 @@
       </c>
     </row>
     <row r="86" spans="2:7">
-      <c r="B86" s="48"/>
+      <c r="B86" s="76"/>
       <c r="C86" t="s">
         <v>158</v>
       </c>
@@ -3182,13 +3317,13 @@
       </c>
     </row>
     <row r="87" spans="2:7" ht="19">
-      <c r="B87" s="47" t="s">
+      <c r="B87" s="72" t="s">
         <v>160</v>
       </c>
-      <c r="C87" s="47"/>
-      <c r="D87" s="47"/>
-      <c r="E87" s="47"/>
-      <c r="F87" s="47"/>
+      <c r="C87" s="72"/>
+      <c r="D87" s="72"/>
+      <c r="E87" s="72"/>
+      <c r="F87" s="72"/>
     </row>
     <row r="88" spans="2:7">
       <c r="C88" t="s">
@@ -3210,13 +3345,13 @@
       </c>
     </row>
     <row r="90" spans="2:7" ht="19">
-      <c r="B90" s="47" t="s">
+      <c r="B90" s="72" t="s">
         <v>164</v>
       </c>
-      <c r="C90" s="47"/>
-      <c r="D90" s="47"/>
-      <c r="E90" s="47"/>
-      <c r="F90" s="47"/>
+      <c r="C90" s="72"/>
+      <c r="D90" s="72"/>
+      <c r="E90" s="72"/>
+      <c r="F90" s="72"/>
     </row>
     <row r="91" spans="2:7">
       <c r="C91" t="s">
@@ -3249,13 +3384,13 @@
       </c>
     </row>
     <row r="94" spans="2:7" ht="19">
-      <c r="B94" s="47" t="s">
+      <c r="B94" s="72" t="s">
         <v>171</v>
       </c>
-      <c r="C94" s="47"/>
-      <c r="D94" s="47"/>
-      <c r="E94" s="47"/>
-      <c r="F94" s="47"/>
+      <c r="C94" s="72"/>
+      <c r="D94" s="72"/>
+      <c r="E94" s="72"/>
+      <c r="F94" s="72"/>
     </row>
     <row r="95" spans="2:7">
       <c r="C95" t="s">
@@ -3338,13 +3473,13 @@
       </c>
     </row>
     <row r="103" spans="1:6" ht="19">
-      <c r="B103" s="47" t="s">
+      <c r="B103" s="72" t="s">
         <v>187</v>
       </c>
-      <c r="C103" s="47"/>
-      <c r="D103" s="47"/>
-      <c r="E103" s="47"/>
-      <c r="F103" s="47"/>
+      <c r="C103" s="72"/>
+      <c r="D103" s="72"/>
+      <c r="E103" s="72"/>
+      <c r="F103" s="72"/>
     </row>
     <row r="104" spans="1:6">
       <c r="C104" t="s">
@@ -3395,13 +3530,13 @@
       </c>
     </row>
     <row r="110" spans="1:6" ht="19">
-      <c r="B110" s="47" t="s">
+      <c r="B110" s="72" t="s">
         <v>198</v>
       </c>
-      <c r="C110" s="47"/>
-      <c r="D110" s="47"/>
-      <c r="E110" s="47"/>
-      <c r="F110" s="47"/>
+      <c r="C110" s="72"/>
+      <c r="D110" s="72"/>
+      <c r="E110" s="72"/>
+      <c r="F110" s="72"/>
     </row>
     <row r="111" spans="1:6">
       <c r="C111" t="s">
@@ -3412,7 +3547,7 @@
       </c>
     </row>
     <row r="112" spans="1:6">
-      <c r="B112" s="48" t="s">
+      <c r="B112" s="76" t="s">
         <v>233</v>
       </c>
       <c r="C112" t="s">
@@ -3423,7 +3558,7 @@
       </c>
     </row>
     <row r="113" spans="1:6">
-      <c r="B113" s="48"/>
+      <c r="B113" s="76"/>
       <c r="C113" t="s">
         <v>201</v>
       </c>
@@ -3432,7 +3567,7 @@
       </c>
     </row>
     <row r="114" spans="1:6">
-      <c r="B114" s="48"/>
+      <c r="B114" s="76"/>
       <c r="C114" t="s">
         <v>203</v>
       </c>
@@ -3441,7 +3576,7 @@
       </c>
     </row>
     <row r="115" spans="1:6">
-      <c r="B115" s="48"/>
+      <c r="B115" s="76"/>
       <c r="C115" t="s">
         <v>205</v>
       </c>
@@ -3453,7 +3588,7 @@
       </c>
     </row>
     <row r="116" spans="1:6">
-      <c r="B116" s="48"/>
+      <c r="B116" s="76"/>
       <c r="C116" t="s">
         <v>207</v>
       </c>
@@ -3473,13 +3608,13 @@
       </c>
     </row>
     <row r="118" spans="1:6" ht="19">
-      <c r="B118" s="47" t="s">
+      <c r="B118" s="72" t="s">
         <v>213</v>
       </c>
-      <c r="C118" s="47"/>
-      <c r="D118" s="47"/>
-      <c r="E118" s="47"/>
-      <c r="F118" s="47"/>
+      <c r="C118" s="72"/>
+      <c r="D118" s="72"/>
+      <c r="E118" s="72"/>
+      <c r="F118" s="72"/>
     </row>
     <row r="119" spans="1:6">
       <c r="C119" t="s">
@@ -3520,13 +3655,13 @@
       </c>
     </row>
     <row r="123" spans="1:6" ht="19">
-      <c r="B123" s="47" t="s">
+      <c r="B123" s="72" t="s">
         <v>224</v>
       </c>
-      <c r="C123" s="47"/>
-      <c r="D123" s="47"/>
-      <c r="E123" s="47"/>
-      <c r="F123" s="47"/>
+      <c r="C123" s="72"/>
+      <c r="D123" s="72"/>
+      <c r="E123" s="72"/>
+      <c r="F123" s="72"/>
     </row>
     <row r="124" spans="1:6">
       <c r="C124" t="s">
@@ -3553,13 +3688,13 @@
       </c>
     </row>
     <row r="127" spans="1:6" ht="19">
-      <c r="B127" s="47" t="s">
+      <c r="B127" s="72" t="s">
         <v>225</v>
       </c>
-      <c r="C127" s="47"/>
-      <c r="D127" s="47"/>
-      <c r="E127" s="47"/>
-      <c r="F127" s="47"/>
+      <c r="C127" s="72"/>
+      <c r="D127" s="72"/>
+      <c r="E127" s="72"/>
+      <c r="F127" s="72"/>
     </row>
     <row r="128" spans="1:6">
       <c r="C128" t="s">
@@ -3570,7 +3705,7 @@
       </c>
     </row>
     <row r="129" spans="2:4">
-      <c r="B129" s="48" t="s">
+      <c r="B129" s="76" t="s">
         <v>232</v>
       </c>
       <c r="C129" t="s">
@@ -3581,7 +3716,7 @@
       </c>
     </row>
     <row r="130" spans="2:4">
-      <c r="B130" s="48"/>
+      <c r="B130" s="76"/>
       <c r="C130" t="s">
         <v>227</v>
       </c>
@@ -3590,7 +3725,7 @@
       </c>
     </row>
     <row r="131" spans="2:4">
-      <c r="B131" s="48"/>
+      <c r="B131" s="76"/>
       <c r="C131" t="s">
         <v>228</v>
       </c>
@@ -3600,20 +3735,6 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="B42:F42"/>
-    <mergeCell ref="B54:F54"/>
-    <mergeCell ref="C1:G1"/>
-    <mergeCell ref="C2:F2"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="G13:G14"/>
-    <mergeCell ref="B17:G17"/>
-    <mergeCell ref="B129:B131"/>
-    <mergeCell ref="B87:F87"/>
-    <mergeCell ref="B90:F90"/>
-    <mergeCell ref="B94:F94"/>
-    <mergeCell ref="B103:F103"/>
-    <mergeCell ref="B110:F110"/>
-    <mergeCell ref="B118:F118"/>
     <mergeCell ref="A12:A16"/>
     <mergeCell ref="A52:A53"/>
     <mergeCell ref="B123:F123"/>
@@ -3630,6 +3751,20 @@
     <mergeCell ref="B30:F30"/>
     <mergeCell ref="B34:F34"/>
     <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B129:B131"/>
+    <mergeCell ref="B87:F87"/>
+    <mergeCell ref="B90:F90"/>
+    <mergeCell ref="B94:F94"/>
+    <mergeCell ref="B103:F103"/>
+    <mergeCell ref="B110:F110"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B42:F42"/>
+    <mergeCell ref="B54:F54"/>
+    <mergeCell ref="C1:G1"/>
+    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="B17:G17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -3651,24 +3786,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="27">
-      <c r="C1" s="49" t="s">
+      <c r="C1" s="73" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="73"/>
     </row>
     <row r="2" spans="1:7" ht="19">
       <c r="A2" t="s">
         <v>236</v>
       </c>
-      <c r="C2" s="47" t="s">
+      <c r="C2" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="72"/>
     </row>
     <row r="3" spans="1:7">
       <c r="B3" s="11">
@@ -3765,16 +3900,16 @@
       </c>
     </row>
     <row r="9" spans="1:7" ht="19">
-      <c r="B9" s="47" t="s">
+      <c r="B9" s="72" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="47"/>
-      <c r="D9" s="47"/>
-      <c r="E9" s="47"/>
-      <c r="F9" s="47"/>
+      <c r="C9" s="72"/>
+      <c r="D9" s="72"/>
+      <c r="E9" s="72"/>
+      <c r="F9" s="72"/>
     </row>
     <row r="10" spans="1:7" ht="19">
-      <c r="A10" s="45" t="s">
+      <c r="A10" s="77" t="s">
         <v>234</v>
       </c>
       <c r="B10" s="24"/>
@@ -3788,7 +3923,7 @@
       <c r="F10" s="26"/>
     </row>
     <row r="11" spans="1:7" ht="34" customHeight="1">
-      <c r="A11" s="45"/>
+      <c r="A11" s="77"/>
       <c r="B11" s="27">
         <v>9</v>
       </c>
@@ -3802,12 +3937,12 @@
       <c r="F11" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="G11" s="51" t="s">
+      <c r="G11" s="74" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="34">
-      <c r="A12" s="45"/>
+      <c r="A12" s="77"/>
       <c r="B12" s="27">
         <v>10</v>
       </c>
@@ -3821,10 +3956,10 @@
       <c r="F12" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="G12" s="52"/>
+      <c r="G12" s="75"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="45"/>
+      <c r="A13" s="77"/>
       <c r="B13" s="27">
         <v>11</v>
       </c>
@@ -3840,7 +3975,7 @@
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="45"/>
+      <c r="A14" s="77"/>
       <c r="B14" s="27">
         <v>12</v>
       </c>
@@ -3854,14 +3989,14 @@
       <c r="F14" s="25"/>
     </row>
     <row r="15" spans="1:7" ht="27">
-      <c r="B15" s="49" t="s">
+      <c r="B15" s="73" t="s">
         <v>39</v>
       </c>
-      <c r="C15" s="49"/>
-      <c r="D15" s="49"/>
-      <c r="E15" s="49"/>
-      <c r="F15" s="49"/>
-      <c r="G15" s="49"/>
+      <c r="C15" s="73"/>
+      <c r="D15" s="73"/>
+      <c r="E15" s="73"/>
+      <c r="F15" s="73"/>
+      <c r="G15" s="73"/>
     </row>
     <row r="16" spans="1:7" ht="27">
       <c r="B16" s="22"/>
@@ -4012,23 +4147,23 @@
       <c r="F26" s="9"/>
     </row>
     <row r="27" spans="1:7" ht="27">
-      <c r="B27" s="49" t="s">
+      <c r="B27" s="73" t="s">
         <v>60</v>
       </c>
-      <c r="C27" s="49"/>
-      <c r="D27" s="49"/>
-      <c r="E27" s="49"/>
-      <c r="F27" s="49"/>
-      <c r="G27" s="49"/>
+      <c r="C27" s="73"/>
+      <c r="D27" s="73"/>
+      <c r="E27" s="73"/>
+      <c r="F27" s="73"/>
+      <c r="G27" s="73"/>
     </row>
     <row r="28" spans="1:7" ht="19">
-      <c r="B28" s="47" t="s">
+      <c r="B28" s="72" t="s">
         <v>61</v>
       </c>
-      <c r="C28" s="47"/>
-      <c r="D28" s="47"/>
-      <c r="E28" s="47"/>
-      <c r="F28" s="47"/>
+      <c r="C28" s="72"/>
+      <c r="D28" s="72"/>
+      <c r="E28" s="72"/>
+      <c r="F28" s="72"/>
     </row>
     <row r="29" spans="1:7" ht="19">
       <c r="B29" s="43"/>
@@ -4071,13 +4206,13 @@
       </c>
     </row>
     <row r="32" spans="1:7" ht="19">
-      <c r="B32" s="47" t="s">
+      <c r="B32" s="72" t="s">
         <v>67</v>
       </c>
-      <c r="C32" s="47"/>
-      <c r="D32" s="47"/>
-      <c r="E32" s="47"/>
-      <c r="F32" s="47"/>
+      <c r="C32" s="72"/>
+      <c r="D32" s="72"/>
+      <c r="E32" s="72"/>
+      <c r="F32" s="72"/>
     </row>
     <row r="33" spans="2:7">
       <c r="B33" s="11"/>
@@ -4104,13 +4239,13 @@
       <c r="F34" s="9"/>
     </row>
     <row r="35" spans="2:7" ht="19">
-      <c r="B35" s="47" t="s">
+      <c r="B35" s="72" t="s">
         <v>71</v>
       </c>
-      <c r="C35" s="47"/>
-      <c r="D35" s="47"/>
-      <c r="E35" s="47"/>
-      <c r="F35" s="47"/>
+      <c r="C35" s="72"/>
+      <c r="D35" s="72"/>
+      <c r="E35" s="72"/>
+      <c r="F35" s="72"/>
     </row>
     <row r="36" spans="2:7">
       <c r="B36" s="34"/>
@@ -4148,13 +4283,13 @@
       <c r="F38" s="35"/>
     </row>
     <row r="39" spans="2:7" ht="19">
-      <c r="B39" s="50" t="s">
+      <c r="B39" s="71" t="s">
         <v>88</v>
       </c>
-      <c r="C39" s="50"/>
-      <c r="D39" s="50"/>
-      <c r="E39" s="50"/>
-      <c r="F39" s="50"/>
+      <c r="C39" s="71"/>
+      <c r="D39" s="71"/>
+      <c r="E39" s="71"/>
+      <c r="F39" s="71"/>
     </row>
     <row r="40" spans="2:7">
       <c r="B40" s="11"/>
@@ -4243,13 +4378,13 @@
       </c>
     </row>
     <row r="46" spans="2:7" ht="19">
-      <c r="B46" s="47" t="s">
+      <c r="B46" s="72" t="s">
         <v>104</v>
       </c>
-      <c r="C46" s="47"/>
-      <c r="D46" s="47"/>
-      <c r="E46" s="47"/>
-      <c r="F46" s="47"/>
+      <c r="C46" s="72"/>
+      <c r="D46" s="72"/>
+      <c r="E46" s="72"/>
+      <c r="F46" s="72"/>
     </row>
     <row r="47" spans="2:7">
       <c r="C47" t="s">
@@ -4274,13 +4409,13 @@
       </c>
     </row>
     <row r="49" spans="1:7" ht="19">
-      <c r="B49" s="47" t="s">
+      <c r="B49" s="72" t="s">
         <v>108</v>
       </c>
-      <c r="C49" s="47"/>
-      <c r="D49" s="47"/>
-      <c r="E49" s="47"/>
-      <c r="F49" s="47"/>
+      <c r="C49" s="72"/>
+      <c r="D49" s="72"/>
+      <c r="E49" s="72"/>
+      <c r="F49" s="72"/>
     </row>
     <row r="50" spans="1:7">
       <c r="C50" t="s">
@@ -4305,23 +4440,23 @@
       </c>
     </row>
     <row r="52" spans="1:7" ht="27">
-      <c r="B52" s="49" t="s">
+      <c r="B52" s="73" t="s">
         <v>114</v>
       </c>
-      <c r="C52" s="49"/>
-      <c r="D52" s="49"/>
-      <c r="E52" s="49"/>
-      <c r="F52" s="49"/>
-      <c r="G52" s="49"/>
+      <c r="C52" s="73"/>
+      <c r="D52" s="73"/>
+      <c r="E52" s="73"/>
+      <c r="F52" s="73"/>
+      <c r="G52" s="73"/>
     </row>
     <row r="53" spans="1:7" ht="19">
-      <c r="B53" s="47" t="s">
+      <c r="B53" s="72" t="s">
         <v>115</v>
       </c>
-      <c r="C53" s="47"/>
-      <c r="D53" s="47"/>
-      <c r="E53" s="47"/>
-      <c r="F53" s="47"/>
+      <c r="C53" s="72"/>
+      <c r="D53" s="72"/>
+      <c r="E53" s="72"/>
+      <c r="F53" s="72"/>
     </row>
     <row r="54" spans="1:7">
       <c r="C54" t="s">
@@ -4408,13 +4543,13 @@
       </c>
     </row>
     <row r="60" spans="1:7" ht="19">
-      <c r="B60" s="47" t="s">
+      <c r="B60" s="72" t="s">
         <v>128</v>
       </c>
-      <c r="C60" s="47"/>
-      <c r="D60" s="47"/>
-      <c r="E60" s="47"/>
-      <c r="F60" s="47"/>
+      <c r="C60" s="72"/>
+      <c r="D60" s="72"/>
+      <c r="E60" s="72"/>
+      <c r="F60" s="72"/>
     </row>
     <row r="61" spans="1:7">
       <c r="C61" t="s">
@@ -4489,13 +4624,13 @@
       </c>
     </row>
     <row r="67" spans="2:7" ht="19">
-      <c r="B67" s="47" t="s">
+      <c r="B67" s="72" t="s">
         <v>142</v>
       </c>
-      <c r="C67" s="47"/>
-      <c r="D67" s="47"/>
-      <c r="E67" s="47"/>
-      <c r="F67" s="47"/>
+      <c r="C67" s="72"/>
+      <c r="D67" s="72"/>
+      <c r="E67" s="72"/>
+      <c r="F67" s="72"/>
     </row>
     <row r="68" spans="2:7">
       <c r="C68" t="s">
@@ -4544,13 +4679,13 @@
       </c>
     </row>
     <row r="73" spans="2:7" ht="19">
-      <c r="B73" s="47" t="s">
+      <c r="B73" s="72" t="s">
         <v>147</v>
       </c>
-      <c r="C73" s="47"/>
-      <c r="D73" s="47"/>
-      <c r="E73" s="47"/>
-      <c r="F73" s="47"/>
+      <c r="C73" s="72"/>
+      <c r="D73" s="72"/>
+      <c r="E73" s="72"/>
+      <c r="F73" s="72"/>
     </row>
     <row r="74" spans="2:7">
       <c r="C74" t="s">
@@ -4654,13 +4789,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="19">
-      <c r="B85" s="47" t="s">
+      <c r="B85" s="72" t="s">
         <v>160</v>
       </c>
-      <c r="C85" s="47"/>
-      <c r="D85" s="47"/>
-      <c r="E85" s="47"/>
-      <c r="F85" s="47"/>
+      <c r="C85" s="72"/>
+      <c r="D85" s="72"/>
+      <c r="E85" s="72"/>
+      <c r="F85" s="72"/>
     </row>
     <row r="86" spans="2:6">
       <c r="C86" t="s">
@@ -4685,13 +4820,13 @@
       </c>
     </row>
     <row r="88" spans="2:6" ht="19">
-      <c r="B88" s="47" t="s">
+      <c r="B88" s="72" t="s">
         <v>164</v>
       </c>
-      <c r="C88" s="47"/>
-      <c r="D88" s="47"/>
-      <c r="E88" s="47"/>
-      <c r="F88" s="47"/>
+      <c r="C88" s="72"/>
+      <c r="D88" s="72"/>
+      <c r="E88" s="72"/>
+      <c r="F88" s="72"/>
     </row>
     <row r="89" spans="2:6">
       <c r="C89" t="s">
@@ -4727,13 +4862,13 @@
       </c>
     </row>
     <row r="92" spans="2:6" ht="19">
-      <c r="B92" s="47" t="s">
+      <c r="B92" s="72" t="s">
         <v>171</v>
       </c>
-      <c r="C92" s="47"/>
-      <c r="D92" s="47"/>
-      <c r="E92" s="47"/>
-      <c r="F92" s="47"/>
+      <c r="C92" s="72"/>
+      <c r="D92" s="72"/>
+      <c r="E92" s="72"/>
+      <c r="F92" s="72"/>
     </row>
     <row r="93" spans="2:6">
       <c r="C93" t="s">
@@ -4799,13 +4934,13 @@
       </c>
     </row>
     <row r="99" spans="2:6" ht="19">
-      <c r="B99" s="47" t="s">
+      <c r="B99" s="72" t="s">
         <v>187</v>
       </c>
-      <c r="C99" s="47"/>
-      <c r="D99" s="47"/>
-      <c r="E99" s="47"/>
-      <c r="F99" s="47"/>
+      <c r="C99" s="72"/>
+      <c r="D99" s="72"/>
+      <c r="E99" s="72"/>
+      <c r="F99" s="72"/>
     </row>
     <row r="100" spans="2:6">
       <c r="C100" t="s">
@@ -4871,13 +5006,13 @@
       </c>
     </row>
     <row r="106" spans="2:6" ht="19">
-      <c r="B106" s="47" t="s">
+      <c r="B106" s="72" t="s">
         <v>198</v>
       </c>
-      <c r="C106" s="47"/>
-      <c r="D106" s="47"/>
-      <c r="E106" s="47"/>
-      <c r="F106" s="47"/>
+      <c r="C106" s="72"/>
+      <c r="D106" s="72"/>
+      <c r="E106" s="72"/>
+      <c r="F106" s="72"/>
     </row>
     <row r="107" spans="2:6">
       <c r="C107" t="s">
@@ -4960,13 +5095,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="19">
-      <c r="B114" s="47" t="s">
+      <c r="B114" s="72" t="s">
         <v>213</v>
       </c>
-      <c r="C114" s="47"/>
-      <c r="D114" s="47"/>
-      <c r="E114" s="47"/>
-      <c r="F114" s="47"/>
+      <c r="C114" s="72"/>
+      <c r="D114" s="72"/>
+      <c r="E114" s="72"/>
+      <c r="F114" s="72"/>
     </row>
     <row r="115" spans="2:6">
       <c r="C115" t="s">
@@ -4999,13 +5134,13 @@
       </c>
     </row>
     <row r="118" spans="2:6" ht="19">
-      <c r="B118" s="47" t="s">
+      <c r="B118" s="72" t="s">
         <v>224</v>
       </c>
-      <c r="C118" s="47"/>
-      <c r="D118" s="47"/>
-      <c r="E118" s="47"/>
-      <c r="F118" s="47"/>
+      <c r="C118" s="72"/>
+      <c r="D118" s="72"/>
+      <c r="E118" s="72"/>
+      <c r="F118" s="72"/>
     </row>
     <row r="119" spans="2:6">
       <c r="C119" t="s">
@@ -5054,13 +5189,13 @@
       </c>
     </row>
     <row r="124" spans="2:6" ht="19">
-      <c r="B124" s="47" t="s">
+      <c r="B124" s="72" t="s">
         <v>225</v>
       </c>
-      <c r="C124" s="47"/>
-      <c r="D124" s="47"/>
-      <c r="E124" s="47"/>
-      <c r="F124" s="47"/>
+      <c r="C124" s="72"/>
+      <c r="D124" s="72"/>
+      <c r="E124" s="72"/>
+      <c r="F124" s="72"/>
     </row>
     <row r="125" spans="2:6">
       <c r="C125" t="s">
@@ -5105,12 +5240,15 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="B15:G15"/>
-    <mergeCell ref="C1:G1"/>
-    <mergeCell ref="C2:F2"/>
-    <mergeCell ref="B9:F9"/>
-    <mergeCell ref="A10:A14"/>
-    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="B106:F106"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B88:F88"/>
+    <mergeCell ref="B92:F92"/>
+    <mergeCell ref="B99:F99"/>
     <mergeCell ref="B67:F67"/>
     <mergeCell ref="B27:G27"/>
     <mergeCell ref="B28:F28"/>
@@ -5122,15 +5260,12 @@
     <mergeCell ref="B52:G52"/>
     <mergeCell ref="B53:F53"/>
     <mergeCell ref="B60:F60"/>
-    <mergeCell ref="B106:F106"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B88:F88"/>
-    <mergeCell ref="B92:F92"/>
-    <mergeCell ref="B99:F99"/>
+    <mergeCell ref="B15:G15"/>
+    <mergeCell ref="C1:G1"/>
+    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="B9:F9"/>
+    <mergeCell ref="A10:A14"/>
+    <mergeCell ref="G11:G12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -5142,431 +5277,431 @@
   <dimension ref="A1:G131"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="18.5" style="56" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" style="55"/>
-    <col min="3" max="3" width="22.1640625" style="54" customWidth="1"/>
-    <col min="4" max="4" width="45.33203125" style="53" customWidth="1"/>
-    <col min="5" max="5" width="22.5" style="53" customWidth="1"/>
-    <col min="6" max="6" width="37.6640625" style="53" customWidth="1"/>
+    <col min="1" max="1" width="18.5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" style="5"/>
+    <col min="3" max="3" width="22.1640625" style="6" customWidth="1"/>
+    <col min="4" max="4" width="45.33203125" customWidth="1"/>
+    <col min="5" max="5" width="22.5" customWidth="1"/>
+    <col min="6" max="6" width="37.6640625" customWidth="1"/>
     <col min="7" max="7" width="78.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="27">
-      <c r="C1" s="49" t="s">
+      <c r="C1" s="73" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="73"/>
     </row>
     <row r="2" spans="1:7" ht="19">
-      <c r="A2" s="80" t="s">
+      <c r="A2" s="62" t="s">
         <v>275</v>
       </c>
-      <c r="B2" s="80" t="s">
+      <c r="B2" s="62" t="s">
         <v>274</v>
       </c>
-      <c r="C2" s="63" t="s">
+      <c r="C2" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="63"/>
-      <c r="E2" s="63"/>
-      <c r="F2" s="63"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="72"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="56">
+      <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3" s="55">
+      <c r="B3" s="5">
         <v>1</v>
       </c>
-      <c r="C3" s="76" t="s">
+      <c r="C3" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="64" t="s">
+      <c r="D3" s="51" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="56">
+      <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4" s="55">
+      <c r="B4" s="5">
         <v>2</v>
       </c>
-      <c r="C4" s="76" t="s">
+      <c r="C4" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="65" t="s">
+      <c r="D4" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="56" t="s">
+      <c r="E4" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="56">
+      <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B5" s="55">
+      <c r="B5" s="5">
         <v>3</v>
       </c>
-      <c r="C5" s="76" t="s">
+      <c r="C5" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="64" t="s">
+      <c r="D5" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="56" t="s">
+      <c r="E5" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:7" s="6" customFormat="1" ht="68">
-      <c r="A6" s="55">
+      <c r="A6" s="5">
         <v>4</v>
       </c>
-      <c r="B6" s="55">
+      <c r="B6" s="5">
         <v>4</v>
       </c>
-      <c r="C6" s="76" t="s">
+      <c r="C6" s="58" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="66" t="s">
+      <c r="D6" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="55" t="s">
+      <c r="E6" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="67" t="s">
+      <c r="F6" s="54" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:7" s="5" customFormat="1" ht="102">
-      <c r="A7" s="55">
+      <c r="A7" s="5">
         <v>5</v>
       </c>
-      <c r="B7" s="55">
+      <c r="B7" s="5">
         <v>5</v>
       </c>
-      <c r="C7" s="76" t="s">
+      <c r="C7" s="58" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="66" t="s">
+      <c r="D7" s="53" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="55" t="s">
+      <c r="E7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="68" t="s">
+      <c r="F7" s="55" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:7" s="1" customFormat="1" ht="17">
-      <c r="A8" s="56">
+      <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="B8" s="55">
+      <c r="B8" s="5">
         <v>6</v>
       </c>
-      <c r="C8" s="77" t="s">
+      <c r="C8" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="64" t="s">
+      <c r="D8" s="51" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="59" t="s">
+      <c r="E8" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="F8" s="69" t="s">
+      <c r="F8" s="56" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="19">
-      <c r="B9" s="47" t="s">
+      <c r="B9" s="72" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="47"/>
-      <c r="D9" s="47"/>
-      <c r="E9" s="47"/>
-      <c r="F9" s="47"/>
+      <c r="C9" s="72"/>
+      <c r="D9" s="72"/>
+      <c r="E9" s="72"/>
+      <c r="F9" s="72"/>
     </row>
     <row r="10" spans="1:7" ht="19">
-      <c r="A10" s="58"/>
-      <c r="B10" s="60"/>
-      <c r="C10" s="76" t="s">
+      <c r="A10" s="46"/>
+      <c r="B10" s="48"/>
+      <c r="C10" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="D10" s="53" t="s">
+      <c r="D10" t="s">
         <v>68</v>
       </c>
-      <c r="E10" s="70"/>
-      <c r="F10" s="70"/>
+      <c r="E10" s="45"/>
+      <c r="F10" s="45"/>
     </row>
     <row r="11" spans="1:7" ht="34" customHeight="1">
-      <c r="A11" s="58">
+      <c r="A11" s="46">
         <v>7</v>
       </c>
-      <c r="B11" s="55">
+      <c r="B11" s="5">
         <v>7</v>
       </c>
-      <c r="C11" s="78" t="s">
+      <c r="C11" s="60" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="71" t="s">
+      <c r="D11" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F11" s="55" t="s">
+      <c r="F11" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="G11" s="51" t="s">
+      <c r="G11" s="74" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="34">
-      <c r="A12" s="58">
+      <c r="A12" s="46">
         <v>8</v>
       </c>
-      <c r="B12" s="55">
+      <c r="B12" s="5">
         <v>8</v>
       </c>
-      <c r="C12" s="77" t="s">
+      <c r="C12" s="59" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="71" t="s">
+      <c r="D12" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="F12" s="55" t="s">
+      <c r="F12" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="G12" s="52"/>
+      <c r="G12" s="75"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="58">
+      <c r="A13" s="46">
         <v>9</v>
       </c>
-      <c r="B13" s="55">
+      <c r="B13" s="5">
         <v>9</v>
       </c>
-      <c r="C13" s="77" t="s">
+      <c r="C13" s="59" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="53" t="s">
+      <c r="D13" t="s">
         <v>32</v>
       </c>
-      <c r="F13" s="53" t="s">
+      <c r="F13" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="58"/>
-      <c r="B14" s="55">
+      <c r="A14" s="46"/>
+      <c r="B14" s="5">
         <v>10</v>
       </c>
-      <c r="C14" s="77" t="s">
+      <c r="C14" s="59" t="s">
         <v>35</v>
       </c>
-      <c r="D14" s="53" t="s">
+      <c r="D14" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="27">
-      <c r="B15" s="49" t="s">
+      <c r="B15" s="73" t="s">
         <v>39</v>
       </c>
-      <c r="C15" s="49"/>
-      <c r="D15" s="49"/>
-      <c r="E15" s="49"/>
-      <c r="F15" s="49"/>
-      <c r="G15" s="49"/>
+      <c r="C15" s="73"/>
+      <c r="D15" s="73"/>
+      <c r="E15" s="73"/>
+      <c r="F15" s="73"/>
+      <c r="G15" s="73"/>
     </row>
     <row r="16" spans="1:7" ht="27">
-      <c r="B16" s="61"/>
-      <c r="C16" s="76" t="s">
+      <c r="B16" s="49"/>
+      <c r="C16" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="D16" s="66" t="s">
+      <c r="D16" s="53" t="s">
         <v>68</v>
       </c>
-      <c r="E16" s="72"/>
-      <c r="F16" s="72"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
       <c r="G16" s="2"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="B17" s="55">
+      <c r="B17" s="5">
         <v>11</v>
       </c>
-      <c r="C17" s="76" t="s">
+      <c r="C17" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="D17" s="66" t="s">
+      <c r="D17" s="53" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="56">
+      <c r="A18" s="1">
         <v>10</v>
       </c>
-      <c r="B18" s="55">
+      <c r="B18" s="5">
         <v>12</v>
       </c>
-      <c r="C18" s="76" t="s">
+      <c r="C18" s="58" t="s">
         <v>42</v>
       </c>
-      <c r="D18" s="66" t="s">
+      <c r="D18" s="53" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="56">
+      <c r="A19" s="1">
         <v>11</v>
       </c>
-      <c r="B19" s="55">
+      <c r="B19" s="5">
         <v>13</v>
       </c>
-      <c r="C19" s="76" t="s">
+      <c r="C19" s="58" t="s">
         <v>43</v>
       </c>
-      <c r="D19" s="66" t="s">
+      <c r="D19" s="53" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="56">
+      <c r="A20" s="1">
         <v>12</v>
       </c>
-      <c r="B20" s="55">
+      <c r="B20" s="5">
         <v>14</v>
       </c>
-      <c r="C20" s="76" t="s">
+      <c r="C20" s="58" t="s">
         <v>44</v>
       </c>
-      <c r="D20" s="66" t="s">
+      <c r="D20" s="53" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="21" spans="1:7">
-      <c r="B21" s="55">
+      <c r="B21" s="5">
         <v>15</v>
       </c>
-      <c r="C21" s="76" t="s">
+      <c r="C21" s="58" t="s">
         <v>46</v>
       </c>
-      <c r="D21" s="66" t="s">
+      <c r="D21" s="53" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="56">
+      <c r="A22" s="1">
         <v>13</v>
       </c>
-      <c r="B22" s="55">
+      <c r="B22" s="5">
         <v>16</v>
       </c>
-      <c r="C22" s="76" t="s">
+      <c r="C22" s="58" t="s">
         <v>48</v>
       </c>
-      <c r="D22" s="66" t="s">
+      <c r="D22" s="53" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:7">
-      <c r="B23" s="55">
+      <c r="B23" s="5">
         <v>17</v>
       </c>
-      <c r="C23" s="76" t="s">
+      <c r="C23" s="58" t="s">
         <v>50</v>
       </c>
-      <c r="D23" s="66" t="s">
+      <c r="D23" s="53" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="58"/>
-      <c r="C24" s="76" t="s">
+      <c r="A24" s="46"/>
+      <c r="C24" s="58" t="s">
         <v>52</v>
       </c>
-      <c r="D24" s="66" t="s">
+      <c r="D24" s="53" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="56">
+      <c r="A25" s="1">
         <v>14</v>
       </c>
-      <c r="B25" s="55">
+      <c r="B25" s="5">
         <v>18</v>
       </c>
-      <c r="C25" s="76" t="s">
+      <c r="C25" s="58" t="s">
         <v>54</v>
       </c>
-      <c r="D25" s="66" t="s">
+      <c r="D25" s="53" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="59">
+      <c r="A26" s="47">
         <v>15</v>
       </c>
-      <c r="B26" s="55">
+      <c r="B26" s="5">
         <v>19</v>
       </c>
-      <c r="C26" s="76" t="s">
+      <c r="C26" s="58" t="s">
         <v>56</v>
       </c>
-      <c r="D26" s="66" t="s">
+      <c r="D26" s="53" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="27">
-      <c r="B27" s="49" t="s">
+      <c r="B27" s="73" t="s">
         <v>60</v>
       </c>
-      <c r="C27" s="49"/>
-      <c r="D27" s="49"/>
-      <c r="E27" s="49"/>
-      <c r="F27" s="49"/>
-      <c r="G27" s="49"/>
+      <c r="C27" s="73"/>
+      <c r="D27" s="73"/>
+      <c r="E27" s="73"/>
+      <c r="F27" s="73"/>
+      <c r="G27" s="73"/>
     </row>
     <row r="28" spans="1:7" ht="19">
-      <c r="B28" s="47" t="s">
+      <c r="B28" s="72" t="s">
         <v>61</v>
       </c>
-      <c r="C28" s="47"/>
-      <c r="D28" s="47"/>
-      <c r="E28" s="47"/>
-      <c r="F28" s="47"/>
+      <c r="C28" s="72"/>
+      <c r="D28" s="72"/>
+      <c r="E28" s="72"/>
+      <c r="F28" s="72"/>
     </row>
     <row r="29" spans="1:7" ht="19">
-      <c r="B29" s="62"/>
-      <c r="C29" s="76" t="s">
+      <c r="B29" s="50"/>
+      <c r="C29" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="D29" s="53" t="s">
+      <c r="D29" t="s">
         <v>3</v>
       </c>
-      <c r="E29" s="70"/>
-      <c r="F29" s="70"/>
+      <c r="E29" s="45"/>
+      <c r="F29" s="45"/>
     </row>
     <row r="30" spans="1:7">
-      <c r="C30" s="76" t="s">
+      <c r="C30" s="58" t="s">
         <v>62</v>
       </c>
-      <c r="D30" s="53" t="s">
+      <c r="D30" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="38">
-      <c r="A31" s="56">
+      <c r="A31" s="1">
         <v>16</v>
       </c>
-      <c r="B31" s="55">
+      <c r="B31" s="5">
         <v>20</v>
       </c>
-      <c r="C31" s="76" t="s">
+      <c r="C31" s="58" t="s">
         <v>64</v>
       </c>
-      <c r="D31" s="66" t="s">
+      <c r="D31" s="53" t="s">
         <v>65</v>
       </c>
       <c r="G31" s="18" t="s">
@@ -5574,140 +5709,140 @@
       </c>
     </row>
     <row r="32" spans="1:7" ht="19">
-      <c r="B32" s="47" t="s">
+      <c r="B32" s="72" t="s">
         <v>67</v>
       </c>
-      <c r="C32" s="47"/>
-      <c r="D32" s="47"/>
-      <c r="E32" s="47"/>
-      <c r="F32" s="47"/>
+      <c r="C32" s="72"/>
+      <c r="D32" s="72"/>
+      <c r="E32" s="72"/>
+      <c r="F32" s="72"/>
     </row>
     <row r="33" spans="1:7">
-      <c r="C33" s="76" t="s">
+      <c r="C33" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="D33" s="53" t="s">
+      <c r="D33" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="56">
+      <c r="A34" s="1">
         <v>17</v>
       </c>
-      <c r="B34" s="55">
+      <c r="B34" s="5">
         <v>21</v>
       </c>
-      <c r="C34" s="76" t="s">
+      <c r="C34" s="58" t="s">
         <v>69</v>
       </c>
-      <c r="D34" s="53" t="s">
+      <c r="D34" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="19">
-      <c r="B35" s="47" t="s">
+      <c r="B35" s="72" t="s">
         <v>71</v>
       </c>
-      <c r="C35" s="47"/>
-      <c r="D35" s="47"/>
-      <c r="E35" s="47"/>
-      <c r="F35" s="47"/>
+      <c r="C35" s="72"/>
+      <c r="D35" s="72"/>
+      <c r="E35" s="72"/>
+      <c r="F35" s="72"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="C36" s="76" t="s">
+      <c r="C36" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="D36" s="53" t="s">
+      <c r="D36" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="37" spans="1:7">
-      <c r="C37" s="76" t="s">
+      <c r="C37" s="58" t="s">
         <v>62</v>
       </c>
-      <c r="D37" s="53" t="s">
+      <c r="D37" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="56">
+      <c r="A38" s="1">
         <v>18</v>
       </c>
-      <c r="B38" s="55">
+      <c r="B38" s="5">
         <v>22</v>
       </c>
-      <c r="C38" s="76" t="s">
+      <c r="C38" s="58" t="s">
         <v>74</v>
       </c>
-      <c r="D38" s="53" t="s">
+      <c r="D38" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="19">
-      <c r="B39" s="50" t="s">
+      <c r="B39" s="71" t="s">
         <v>88</v>
       </c>
-      <c r="C39" s="50"/>
-      <c r="D39" s="50"/>
-      <c r="E39" s="50"/>
-      <c r="F39" s="50"/>
+      <c r="C39" s="71"/>
+      <c r="D39" s="71"/>
+      <c r="E39" s="71"/>
+      <c r="F39" s="71"/>
     </row>
     <row r="40" spans="1:7">
-      <c r="C40" s="76" t="s">
+      <c r="C40" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="D40" s="53" t="s">
+      <c r="D40" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="56">
+      <c r="A41" s="1">
         <v>19</v>
       </c>
-      <c r="B41" s="55">
+      <c r="B41" s="5">
         <v>23</v>
       </c>
-      <c r="C41" s="76" t="s">
+      <c r="C41" s="58" t="s">
         <v>81</v>
       </c>
-      <c r="D41" s="53" t="s">
+      <c r="D41" t="s">
         <v>82</v>
       </c>
-      <c r="F41" s="73" t="s">
+      <c r="F41" s="57" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="56">
+      <c r="A42" s="1">
         <v>20</v>
       </c>
-      <c r="B42" s="55">
+      <c r="B42" s="5">
         <v>24</v>
       </c>
-      <c r="C42" s="76" t="s">
+      <c r="C42" s="58" t="s">
         <v>84</v>
       </c>
-      <c r="D42" s="53" t="s">
+      <c r="D42" t="s">
         <v>85</v>
       </c>
-      <c r="F42" s="73" t="s">
+      <c r="F42" s="57" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="18">
-      <c r="A43" s="56">
+      <c r="A43" s="1">
         <v>21</v>
       </c>
-      <c r="B43" s="55">
+      <c r="B43" s="5">
         <v>25</v>
       </c>
-      <c r="C43" s="76" t="s">
+      <c r="C43" s="58" t="s">
         <v>90</v>
       </c>
-      <c r="D43" s="53" t="s">
+      <c r="D43" t="s">
         <v>91</v>
       </c>
-      <c r="F43" s="73" t="s">
+      <c r="F43" s="57" t="s">
         <v>87</v>
       </c>
       <c r="G43" s="17" t="s">
@@ -5715,27 +5850,27 @@
       </c>
     </row>
     <row r="44" spans="1:7">
-      <c r="B44" s="55">
+      <c r="B44" s="5">
         <v>26</v>
       </c>
-      <c r="C44" s="76" t="s">
+      <c r="C44" s="58" t="s">
         <v>93</v>
       </c>
-      <c r="D44" s="53" t="s">
+      <c r="D44" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="17">
-      <c r="A45" s="56">
+      <c r="A45" s="1">
         <v>22</v>
       </c>
-      <c r="B45" s="55">
+      <c r="B45" s="5">
         <v>27</v>
       </c>
-      <c r="C45" s="76" t="s">
+      <c r="C45" s="58" t="s">
         <v>95</v>
       </c>
-      <c r="D45" s="53" t="s">
+      <c r="D45" t="s">
         <v>96</v>
       </c>
       <c r="G45" s="4" t="s">
@@ -5743,33 +5878,33 @@
       </c>
     </row>
     <row r="46" spans="1:7" ht="19">
-      <c r="B46" s="47" t="s">
+      <c r="B46" s="72" t="s">
         <v>104</v>
       </c>
-      <c r="C46" s="47"/>
-      <c r="D46" s="47"/>
-      <c r="E46" s="47"/>
-      <c r="F46" s="47"/>
+      <c r="C46" s="72"/>
+      <c r="D46" s="72"/>
+      <c r="E46" s="72"/>
+      <c r="F46" s="72"/>
     </row>
     <row r="47" spans="1:7">
-      <c r="C47" s="76" t="s">
+      <c r="C47" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="D47" s="53" t="s">
+      <c r="D47" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="18">
-      <c r="A48" s="56" t="s">
+      <c r="A48" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="B48" s="55">
+      <c r="B48" s="5">
         <v>28</v>
       </c>
-      <c r="C48" s="76" t="s">
+      <c r="C48" s="58" t="s">
         <v>105</v>
       </c>
-      <c r="D48" s="53" t="s">
+      <c r="D48" t="s">
         <v>106</v>
       </c>
       <c r="G48" s="17" t="s">
@@ -5777,33 +5912,33 @@
       </c>
     </row>
     <row r="49" spans="1:7" ht="19">
-      <c r="B49" s="47" t="s">
+      <c r="B49" s="72" t="s">
         <v>108</v>
       </c>
-      <c r="C49" s="47"/>
-      <c r="D49" s="47"/>
-      <c r="E49" s="47"/>
-      <c r="F49" s="47"/>
+      <c r="C49" s="72"/>
+      <c r="D49" s="72"/>
+      <c r="E49" s="72"/>
+      <c r="F49" s="72"/>
     </row>
     <row r="50" spans="1:7">
-      <c r="C50" s="76" t="s">
+      <c r="C50" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="D50" s="53" t="s">
+      <c r="D50" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="51" spans="1:7">
-      <c r="A51" s="56" t="s">
+      <c r="A51" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="B51" s="55">
+      <c r="B51" s="5">
         <v>29</v>
       </c>
-      <c r="C51" s="76" t="s">
+      <c r="C51" s="58" t="s">
         <v>111</v>
       </c>
-      <c r="D51" s="53" t="s">
+      <c r="D51" t="s">
         <v>112</v>
       </c>
       <c r="G51" t="s">
@@ -5811,294 +5946,294 @@
       </c>
     </row>
     <row r="52" spans="1:7" ht="27">
-      <c r="B52" s="49" t="s">
+      <c r="B52" s="73" t="s">
         <v>114</v>
       </c>
-      <c r="C52" s="49"/>
-      <c r="D52" s="49"/>
-      <c r="E52" s="49"/>
-      <c r="F52" s="49"/>
-      <c r="G52" s="49"/>
+      <c r="C52" s="73"/>
+      <c r="D52" s="73"/>
+      <c r="E52" s="73"/>
+      <c r="F52" s="73"/>
+      <c r="G52" s="73"/>
     </row>
     <row r="53" spans="1:7" ht="19">
-      <c r="B53" s="47" t="s">
+      <c r="B53" s="72" t="s">
         <v>115</v>
       </c>
-      <c r="C53" s="47"/>
-      <c r="D53" s="47"/>
-      <c r="E53" s="47"/>
-      <c r="F53" s="47"/>
+      <c r="C53" s="72"/>
+      <c r="D53" s="72"/>
+      <c r="E53" s="72"/>
+      <c r="F53" s="72"/>
     </row>
     <row r="54" spans="1:7">
-      <c r="C54" s="76" t="s">
+      <c r="C54" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="D54" s="53" t="s">
+      <c r="D54" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="55" spans="1:7">
-      <c r="A55" s="57" t="s">
+      <c r="A55" s="80" t="s">
         <v>279</v>
       </c>
-      <c r="B55" s="55">
+      <c r="B55" s="5">
         <v>30</v>
       </c>
-      <c r="C55" s="76" t="s">
+      <c r="C55" s="58" t="s">
         <v>116</v>
       </c>
-      <c r="D55" s="53" t="s">
+      <c r="D55" t="s">
         <v>117</v>
       </c>
-      <c r="E55" s="53" t="s">
+      <c r="E55" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="56" spans="1:7">
-      <c r="A56" s="57"/>
-      <c r="B56" s="55">
+      <c r="A56" s="80"/>
+      <c r="B56" s="5">
         <v>31</v>
       </c>
-      <c r="C56" s="76" t="s">
+      <c r="C56" s="58" t="s">
         <v>118</v>
       </c>
-      <c r="D56" s="53" t="s">
+      <c r="D56" t="s">
         <v>119</v>
       </c>
-      <c r="E56" s="53" t="s">
+      <c r="E56" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="57" spans="1:7">
-      <c r="A57" s="57"/>
-      <c r="B57" s="55">
+      <c r="A57" s="80"/>
+      <c r="B57" s="5">
         <v>32</v>
       </c>
-      <c r="C57" s="76" t="s">
+      <c r="C57" s="58" t="s">
         <v>120</v>
       </c>
-      <c r="D57" s="53" t="s">
+      <c r="D57" t="s">
         <v>121</v>
       </c>
-      <c r="E57" s="53" t="s">
+      <c r="E57" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="58" spans="1:7">
-      <c r="A58" s="57"/>
-      <c r="B58" s="55">
+      <c r="A58" s="80"/>
+      <c r="B58" s="5">
         <v>33</v>
       </c>
-      <c r="C58" s="76" t="s">
+      <c r="C58" s="58" t="s">
         <v>122</v>
       </c>
-      <c r="D58" s="53" t="s">
+      <c r="D58" t="s">
         <v>123</v>
       </c>
-      <c r="E58" s="53" t="s">
+      <c r="E58" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="59" spans="1:7">
-      <c r="A59" s="57"/>
-      <c r="B59" s="55">
+      <c r="A59" s="80"/>
+      <c r="B59" s="5">
         <v>34</v>
       </c>
-      <c r="C59" s="76" t="s">
+      <c r="C59" s="58" t="s">
         <v>243</v>
       </c>
-      <c r="D59" s="53" t="s">
+      <c r="D59" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="19">
-      <c r="B60" s="47" t="s">
+      <c r="B60" s="72" t="s">
         <v>128</v>
       </c>
-      <c r="C60" s="47"/>
-      <c r="D60" s="47"/>
-      <c r="E60" s="47"/>
-      <c r="F60" s="47"/>
+      <c r="C60" s="72"/>
+      <c r="D60" s="72"/>
+      <c r="E60" s="72"/>
+      <c r="F60" s="72"/>
     </row>
     <row r="61" spans="1:7">
-      <c r="C61" s="76" t="s">
+      <c r="C61" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="D61" s="53" t="s">
+      <c r="D61" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="62" spans="1:7">
-      <c r="A62" s="56">
+      <c r="A62" s="1">
         <v>25</v>
       </c>
-      <c r="B62" s="55">
+      <c r="B62" s="5">
         <v>35</v>
       </c>
-      <c r="C62" s="76" t="s">
+      <c r="C62" s="58" t="s">
         <v>129</v>
       </c>
-      <c r="D62" s="53" t="s">
+      <c r="D62" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="18">
-      <c r="B63" s="55">
+      <c r="B63" s="5">
         <v>36</v>
       </c>
-      <c r="C63" s="76" t="s">
+      <c r="C63" s="58" t="s">
         <v>131</v>
       </c>
-      <c r="D63" s="53" t="s">
+      <c r="D63" t="s">
         <v>132</v>
       </c>
-      <c r="F63" s="74" t="s">
+      <c r="F63" s="17" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="64" spans="1:7">
-      <c r="B64" s="55">
+      <c r="B64" s="5">
         <v>37</v>
       </c>
-      <c r="C64" s="76" t="s">
+      <c r="C64" s="58" t="s">
         <v>247</v>
       </c>
-      <c r="D64" s="53" t="s">
+      <c r="D64" t="s">
         <v>135</v>
       </c>
-      <c r="F64" s="53" t="s">
+      <c r="F64" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="65" spans="1:7">
-      <c r="A65" s="56">
+      <c r="A65" s="1">
         <v>26</v>
       </c>
-      <c r="B65" s="55">
+      <c r="B65" s="5">
         <v>38</v>
       </c>
-      <c r="C65" s="76" t="s">
+      <c r="C65" s="58" t="s">
         <v>134</v>
       </c>
-      <c r="D65" s="53" t="s">
+      <c r="D65" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="66" spans="1:7">
-      <c r="B66" s="55">
+      <c r="B66" s="5">
         <v>39</v>
       </c>
-      <c r="C66" s="76" t="s">
+      <c r="C66" s="58" t="s">
         <v>246</v>
       </c>
-      <c r="D66" s="53" t="s">
+      <c r="D66" t="s">
         <v>138</v>
       </c>
-      <c r="F66" s="53" t="s">
+      <c r="F66" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="19">
-      <c r="B67" s="47" t="s">
+      <c r="B67" s="72" t="s">
         <v>142</v>
       </c>
-      <c r="C67" s="47"/>
-      <c r="D67" s="47"/>
-      <c r="E67" s="47"/>
-      <c r="F67" s="47"/>
+      <c r="C67" s="72"/>
+      <c r="D67" s="72"/>
+      <c r="E67" s="72"/>
+      <c r="F67" s="72"/>
     </row>
     <row r="68" spans="1:7">
-      <c r="C68" s="76" t="s">
+      <c r="C68" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="D68" s="53" t="s">
+      <c r="D68" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="69" spans="1:7">
-      <c r="A69" s="82" t="s">
+      <c r="A69" s="63" t="s">
         <v>277</v>
       </c>
-      <c r="B69" s="81">
+      <c r="B69" s="5">
         <v>40</v>
       </c>
-      <c r="C69" s="76" t="s">
+      <c r="C69" s="58" t="s">
         <v>143</v>
       </c>
-      <c r="D69" s="53" t="s">
-        <v>144</v>
+      <c r="D69" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="70" spans="1:7">
-      <c r="B70" s="81">
+      <c r="B70" s="5">
         <v>41</v>
       </c>
-      <c r="C70" s="76" t="s">
+      <c r="C70" s="58" t="s">
         <v>245</v>
       </c>
-      <c r="D70" s="53" t="s">
+      <c r="D70" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="71" spans="1:7">
-      <c r="A71" s="82" t="s">
+      <c r="A71" s="63" t="s">
         <v>277</v>
       </c>
-      <c r="B71" s="81">
+      <c r="B71" s="5">
         <v>42</v>
       </c>
-      <c r="C71" s="76" t="s">
+      <c r="C71" s="58" t="s">
         <v>248</v>
       </c>
-      <c r="D71" s="53" t="s">
+      <c r="D71" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="72" spans="1:7">
-      <c r="A72" s="82" t="s">
+      <c r="A72" s="63" t="s">
         <v>277</v>
       </c>
-      <c r="B72" s="81">
+      <c r="B72" s="5">
         <v>43</v>
       </c>
-      <c r="C72" s="76" t="s">
+      <c r="C72" s="58" t="s">
         <v>251</v>
       </c>
-      <c r="D72" s="53" t="s">
+      <c r="D72" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="73" spans="1:7" ht="19">
-      <c r="B73" s="47" t="s">
+      <c r="B73" s="72" t="s">
         <v>147</v>
       </c>
-      <c r="C73" s="47"/>
-      <c r="D73" s="47"/>
-      <c r="E73" s="47"/>
-      <c r="F73" s="47"/>
+      <c r="C73" s="72"/>
+      <c r="D73" s="72"/>
+      <c r="E73" s="72"/>
+      <c r="F73" s="72"/>
     </row>
     <row r="74" spans="1:7">
-      <c r="C74" s="76" t="s">
+      <c r="C74" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="D74" s="53" t="s">
+      <c r="D74" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="75" spans="1:7">
-      <c r="A75" s="83" t="s">
+      <c r="A75" s="81" t="s">
         <v>278</v>
       </c>
-      <c r="B75" s="84">
+      <c r="B75" s="64">
         <v>44</v>
       </c>
-      <c r="C75" s="85" t="s">
+      <c r="C75" s="65" t="s">
         <v>148</v>
       </c>
-      <c r="D75" s="86" t="s">
+      <c r="D75" s="66" t="s">
         <v>150</v>
       </c>
-      <c r="E75" s="75" t="s">
+      <c r="E75" s="32" t="s">
         <v>149</v>
       </c>
       <c r="G75" t="s">
@@ -6106,624 +6241,640 @@
       </c>
     </row>
     <row r="76" spans="1:7">
-      <c r="A76" s="87"/>
-      <c r="B76" s="88">
+      <c r="A76" s="82"/>
+      <c r="B76" s="5">
         <v>45</v>
       </c>
-      <c r="C76" s="89" t="s">
+      <c r="C76" s="58" t="s">
         <v>152</v>
       </c>
-      <c r="D76" s="90" t="s">
+      <c r="D76" s="67" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="77" spans="1:7">
-      <c r="A77" s="87"/>
-      <c r="B77" s="88">
+      <c r="A77" s="82"/>
+      <c r="B77" s="5">
         <v>46</v>
       </c>
-      <c r="C77" s="89" t="s">
+      <c r="C77" s="58" t="s">
         <v>154</v>
       </c>
-      <c r="D77" s="90" t="s">
+      <c r="D77" s="67" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="78" spans="1:7">
-      <c r="A78" s="87"/>
-      <c r="B78" s="88">
+      <c r="A78" s="82"/>
+      <c r="B78" s="5">
         <v>47</v>
       </c>
-      <c r="C78" s="89" t="s">
+      <c r="C78" s="58" t="s">
         <v>156</v>
       </c>
-      <c r="D78" s="90" t="s">
+      <c r="D78" s="67" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="79" spans="1:7">
-      <c r="A79" s="91"/>
-      <c r="B79" s="92">
+      <c r="A79" s="83"/>
+      <c r="B79" s="68">
         <v>48</v>
       </c>
-      <c r="C79" s="93" t="s">
+      <c r="C79" s="69" t="s">
         <v>158</v>
       </c>
-      <c r="D79" s="94" t="s">
+      <c r="D79" s="70" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="80" spans="1:7">
-      <c r="A80" s="82" t="s">
+      <c r="A80" s="63" t="s">
         <v>277</v>
       </c>
-      <c r="B80" s="55">
+      <c r="B80" s="5">
         <v>49</v>
       </c>
-      <c r="C80" s="76" t="s">
+      <c r="C80" s="58" t="s">
         <v>252</v>
       </c>
-      <c r="D80" s="53" t="s">
+      <c r="D80" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="81" spans="1:6">
-      <c r="A81" s="82" t="s">
+      <c r="A81" s="63" t="s">
         <v>277</v>
       </c>
-      <c r="B81" s="55">
+      <c r="B81" s="5">
         <v>50</v>
       </c>
-      <c r="C81" s="76" t="s">
+      <c r="C81" s="58" t="s">
         <v>254</v>
       </c>
-      <c r="D81" s="53" t="s">
+      <c r="D81" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="82" spans="1:6">
-      <c r="A82" s="56">
+      <c r="A82" s="84">
         <v>29</v>
       </c>
-      <c r="B82" s="55">
+      <c r="B82" s="85">
         <v>51</v>
       </c>
-      <c r="C82" s="76" t="s">
+      <c r="C82" s="86" t="s">
         <v>256</v>
       </c>
-      <c r="D82" s="53" t="s">
+      <c r="D82" s="87" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="83" spans="1:6">
-      <c r="A83" s="56">
+      <c r="A83" s="1">
         <v>30</v>
       </c>
-      <c r="B83" s="55">
+      <c r="B83" s="5">
         <v>52</v>
       </c>
-      <c r="C83" s="76" t="s">
+      <c r="C83" s="58" t="s">
         <v>272</v>
       </c>
-      <c r="D83" s="53" t="s">
+      <c r="D83" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="85" spans="1:6" ht="19">
-      <c r="B85" s="47" t="s">
+      <c r="B85" s="72" t="s">
         <v>160</v>
       </c>
-      <c r="C85" s="47"/>
-      <c r="D85" s="47"/>
-      <c r="E85" s="47"/>
-      <c r="F85" s="47"/>
+      <c r="C85" s="72"/>
+      <c r="D85" s="72"/>
+      <c r="E85" s="72"/>
+      <c r="F85" s="72"/>
     </row>
     <row r="86" spans="1:6">
-      <c r="C86" s="76" t="s">
+      <c r="C86" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="D86" s="53" t="s">
+      <c r="D86" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="87" spans="1:6" ht="18">
-      <c r="A87" s="56">
+      <c r="A87" s="1">
         <v>31</v>
       </c>
-      <c r="B87" s="55">
+      <c r="B87" s="5">
         <v>53</v>
       </c>
-      <c r="C87" s="76" t="s">
+      <c r="C87" s="58" t="s">
         <v>161</v>
       </c>
-      <c r="D87" s="53" t="s">
+      <c r="D87" t="s">
         <v>162</v>
       </c>
-      <c r="E87" s="74" t="s">
+      <c r="E87" s="17" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="88" spans="1:6" ht="19">
-      <c r="B88" s="47" t="s">
+      <c r="B88" s="72" t="s">
         <v>164</v>
       </c>
-      <c r="C88" s="47"/>
-      <c r="D88" s="47"/>
-      <c r="E88" s="47"/>
-      <c r="F88" s="47"/>
+      <c r="C88" s="72"/>
+      <c r="D88" s="72"/>
+      <c r="E88" s="72"/>
+      <c r="F88" s="72"/>
     </row>
     <row r="89" spans="1:6">
-      <c r="C89" s="76" t="s">
+      <c r="C89" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="D89" s="53" t="s">
+      <c r="D89" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="90" spans="1:6">
-      <c r="C90" s="76" t="s">
+      <c r="C90" s="58" t="s">
         <v>165</v>
       </c>
-      <c r="D90" s="53" t="s">
+      <c r="D90" t="s">
         <v>166</v>
       </c>
-      <c r="E90" s="53" t="s">
+      <c r="E90" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="91" spans="1:6">
-      <c r="C91" s="76" t="s">
+      <c r="C91" s="58" t="s">
         <v>168</v>
       </c>
-      <c r="D91" s="53" t="s">
+      <c r="D91" t="s">
         <v>169</v>
       </c>
-      <c r="E91" s="53" t="s">
+      <c r="E91" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="92" spans="1:6" ht="19">
-      <c r="B92" s="47" t="s">
+      <c r="B92" s="72" t="s">
         <v>171</v>
       </c>
-      <c r="C92" s="47"/>
-      <c r="D92" s="47"/>
-      <c r="E92" s="47"/>
-      <c r="F92" s="47"/>
+      <c r="C92" s="72"/>
+      <c r="D92" s="72"/>
+      <c r="E92" s="72"/>
+      <c r="F92" s="72"/>
     </row>
     <row r="93" spans="1:6">
-      <c r="C93" s="76" t="s">
+      <c r="C93" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="D93" s="53" t="s">
+      <c r="D93" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="94" spans="1:6">
-      <c r="A94" s="56">
+      <c r="A94" s="1">
         <v>32</v>
       </c>
-      <c r="B94" s="55">
+      <c r="B94" s="5">
         <v>54</v>
       </c>
-      <c r="C94" s="76" t="s">
+      <c r="C94" s="58" t="s">
         <v>258</v>
       </c>
-      <c r="D94" s="53" t="s">
+      <c r="D94" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="95" spans="1:6">
-      <c r="A95" s="82" t="s">
+      <c r="A95" s="63" t="s">
         <v>277</v>
       </c>
-      <c r="B95" s="55">
+      <c r="B95" s="5">
         <v>55</v>
       </c>
-      <c r="C95" s="76" t="s">
+      <c r="C95" s="58" t="s">
         <v>259</v>
       </c>
-      <c r="D95" s="53" t="s">
+      <c r="D95" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="96" spans="1:6">
-      <c r="A96" s="82" t="s">
+      <c r="A96" s="63" t="s">
         <v>277</v>
       </c>
-      <c r="B96" s="55">
+      <c r="B96" s="5">
         <v>56</v>
       </c>
-      <c r="C96" s="76" t="s">
+      <c r="C96" s="58" t="s">
         <v>261</v>
       </c>
-      <c r="D96" s="53" t="s">
+      <c r="D96" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="97" spans="1:6">
-      <c r="A97" s="82" t="s">
+      <c r="A97" s="63" t="s">
         <v>277</v>
       </c>
-      <c r="B97" s="55">
+      <c r="B97" s="5">
         <v>57</v>
       </c>
-      <c r="C97" s="76" t="s">
+      <c r="C97" s="58" t="s">
         <v>260</v>
       </c>
-      <c r="D97" s="53" t="s">
+      <c r="D97" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="98" spans="1:6">
-      <c r="A98" s="56">
+      <c r="A98" s="1">
         <v>33</v>
       </c>
-      <c r="B98" s="55">
+      <c r="B98" s="5">
         <v>58</v>
       </c>
-      <c r="C98" s="79" t="s">
+      <c r="C98" s="61" t="s">
         <v>180</v>
       </c>
-      <c r="D98" s="53" t="s">
+      <c r="D98" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="99" spans="1:6" ht="19">
-      <c r="B99" s="47" t="s">
+      <c r="B99" s="72" t="s">
         <v>187</v>
       </c>
-      <c r="C99" s="47"/>
-      <c r="D99" s="47"/>
-      <c r="E99" s="47"/>
-      <c r="F99" s="47"/>
+      <c r="C99" s="72"/>
+      <c r="D99" s="72"/>
+      <c r="E99" s="72"/>
+      <c r="F99" s="72"/>
     </row>
     <row r="100" spans="1:6">
-      <c r="C100" s="76" t="s">
+      <c r="C100" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="D100" s="53" t="s">
+      <c r="D100" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="101" spans="1:6">
-      <c r="A101" s="57" t="s">
+      <c r="A101" s="80" t="s">
         <v>280</v>
       </c>
-      <c r="B101" s="55">
+      <c r="B101" s="5">
         <v>59</v>
       </c>
-      <c r="C101" s="76" t="s">
+      <c r="C101" s="58" t="s">
         <v>188</v>
       </c>
-      <c r="D101" s="53" t="s">
+      <c r="D101" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="102" spans="1:6">
-      <c r="A102" s="57"/>
-      <c r="B102" s="55">
+      <c r="A102" s="80"/>
+      <c r="B102" s="5">
         <v>60</v>
       </c>
-      <c r="C102" s="76" t="s">
+      <c r="C102" s="58" t="s">
         <v>190</v>
       </c>
-      <c r="D102" s="53" t="s">
+      <c r="D102" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="103" spans="1:6">
-      <c r="A103" s="57"/>
-      <c r="B103" s="55">
+      <c r="A103" s="80"/>
+      <c r="B103" s="5">
         <v>61</v>
       </c>
-      <c r="C103" s="76" t="s">
+      <c r="C103" s="58" t="s">
         <v>192</v>
       </c>
-      <c r="D103" s="53" t="s">
+      <c r="D103" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="104" spans="1:6">
-      <c r="A104" s="57"/>
-      <c r="B104" s="55">
+      <c r="A104" s="80"/>
+      <c r="B104" s="5">
         <v>62</v>
       </c>
-      <c r="C104" s="76" t="s">
+      <c r="C104" s="58" t="s">
         <v>194</v>
       </c>
-      <c r="D104" s="53" t="s">
+      <c r="D104" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="105" spans="1:6">
-      <c r="A105" s="57"/>
-      <c r="B105" s="55">
+      <c r="A105" s="80"/>
+      <c r="B105" s="5">
         <v>63</v>
       </c>
-      <c r="C105" s="76" t="s">
+      <c r="C105" s="58" t="s">
         <v>196</v>
       </c>
-      <c r="D105" s="53" t="s">
+      <c r="D105" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="106" spans="1:6" ht="19">
-      <c r="B106" s="47" t="s">
+      <c r="B106" s="72" t="s">
         <v>198</v>
       </c>
-      <c r="C106" s="47"/>
-      <c r="D106" s="47"/>
-      <c r="E106" s="47"/>
-      <c r="F106" s="47"/>
+      <c r="C106" s="72"/>
+      <c r="D106" s="72"/>
+      <c r="E106" s="72"/>
+      <c r="F106" s="72"/>
     </row>
     <row r="107" spans="1:6">
-      <c r="C107" s="76" t="s">
+      <c r="C107" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="D107" s="53" t="s">
+      <c r="D107" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6">
+      <c r="A108" s="80" t="s">
+        <v>281</v>
+      </c>
+      <c r="B108" s="5">
+        <v>64</v>
+      </c>
+      <c r="C108" s="58" t="s">
+        <v>199</v>
+      </c>
+      <c r="D108" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6">
+      <c r="A109" s="80"/>
+      <c r="B109" s="5">
+        <v>65</v>
+      </c>
+      <c r="C109" s="58" t="s">
+        <v>201</v>
+      </c>
+      <c r="D109" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6">
+      <c r="A110" s="80"/>
+      <c r="B110" s="5">
+        <v>66</v>
+      </c>
+      <c r="C110" s="58" t="s">
+        <v>203</v>
+      </c>
+      <c r="D110" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6">
+      <c r="A111" s="80"/>
+      <c r="B111" s="5">
+        <v>67</v>
+      </c>
+      <c r="C111" s="58" t="s">
+        <v>205</v>
+      </c>
+      <c r="D111" t="s">
+        <v>206</v>
+      </c>
+      <c r="E111" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6">
+      <c r="A112" s="80"/>
+      <c r="B112" s="5">
         <v>68</v>
       </c>
-    </row>
-    <row r="108" spans="1:6">
-      <c r="A108" s="57" t="s">
-        <v>281</v>
-      </c>
-      <c r="B108" s="55">
-        <v>64</v>
-      </c>
-      <c r="C108" s="76" t="s">
-        <v>199</v>
-      </c>
-      <c r="D108" s="53" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6">
-      <c r="A109" s="57"/>
-      <c r="B109" s="55">
-        <v>65</v>
-      </c>
-      <c r="C109" s="76" t="s">
-        <v>201</v>
-      </c>
-      <c r="D109" s="53" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6">
-      <c r="A110" s="57"/>
-      <c r="B110" s="55">
-        <v>66</v>
-      </c>
-      <c r="C110" s="76" t="s">
-        <v>203</v>
-      </c>
-      <c r="D110" s="53" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6">
-      <c r="A111" s="57"/>
-      <c r="B111" s="55">
-        <v>67</v>
-      </c>
-      <c r="C111" s="76" t="s">
-        <v>205</v>
-      </c>
-      <c r="D111" s="53" t="s">
-        <v>206</v>
-      </c>
-      <c r="E111" s="53" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6">
-      <c r="A112" s="57"/>
-      <c r="B112" s="55">
+      <c r="C112" s="58" t="s">
+        <v>207</v>
+      </c>
+      <c r="D112" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6">
+      <c r="A113" s="80"/>
+      <c r="B113" s="5">
+        <v>69</v>
+      </c>
+      <c r="C113" s="58" t="s">
+        <v>209</v>
+      </c>
+      <c r="D113" t="s">
+        <v>287</v>
+      </c>
+      <c r="E113" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" ht="19">
+      <c r="B114" s="72" t="s">
+        <v>213</v>
+      </c>
+      <c r="C114" s="72"/>
+      <c r="D114" s="72"/>
+      <c r="E114" s="72"/>
+      <c r="F114" s="72"/>
+    </row>
+    <row r="115" spans="1:6">
+      <c r="C115" s="58" t="s">
+        <v>2</v>
+      </c>
+      <c r="D115" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6">
+      <c r="A116" s="1">
+        <v>38</v>
+      </c>
+      <c r="B116" s="5">
+        <v>70</v>
+      </c>
+      <c r="C116" s="58" t="s">
+        <v>214</v>
+      </c>
+      <c r="D116" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6">
+      <c r="A117" s="63" t="s">
+        <v>277</v>
+      </c>
+      <c r="B117" s="5">
+        <v>71</v>
+      </c>
+      <c r="C117" s="58" t="s">
+        <v>216</v>
+      </c>
+      <c r="D117" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" ht="19">
+      <c r="B118" s="72" t="s">
+        <v>224</v>
+      </c>
+      <c r="C118" s="72"/>
+      <c r="D118" s="72"/>
+      <c r="E118" s="72"/>
+      <c r="F118" s="72"/>
+    </row>
+    <row r="119" spans="1:6">
+      <c r="C119" s="58" t="s">
+        <v>2</v>
+      </c>
+      <c r="D119" t="s">
         <v>68</v>
       </c>
-      <c r="C112" s="76" t="s">
-        <v>207</v>
-      </c>
-      <c r="D112" s="53" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6">
-      <c r="A113" s="57"/>
-      <c r="B113" s="55">
-        <v>69</v>
-      </c>
-      <c r="C113" s="76" t="s">
-        <v>209</v>
-      </c>
-      <c r="D113" s="53" t="s">
-        <v>210</v>
-      </c>
-      <c r="E113" s="53" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" ht="19">
-      <c r="B114" s="47" t="s">
-        <v>213</v>
-      </c>
-      <c r="C114" s="47"/>
-      <c r="D114" s="47"/>
-      <c r="E114" s="47"/>
-      <c r="F114" s="47"/>
-    </row>
-    <row r="115" spans="1:6">
-      <c r="C115" s="76" t="s">
+    </row>
+    <row r="120" spans="1:6">
+      <c r="A120" s="80" t="s">
+        <v>282</v>
+      </c>
+      <c r="B120" s="5">
+        <v>72</v>
+      </c>
+      <c r="C120" s="58" t="s">
+        <v>220</v>
+      </c>
+      <c r="D120" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6">
+      <c r="A121" s="80"/>
+      <c r="B121" s="5">
+        <v>73</v>
+      </c>
+      <c r="C121" s="58" t="s">
+        <v>221</v>
+      </c>
+      <c r="D121" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6">
+      <c r="A122" s="80"/>
+      <c r="B122" s="5">
+        <v>74</v>
+      </c>
+      <c r="C122" s="58" t="s">
+        <v>268</v>
+      </c>
+      <c r="D122" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6">
+      <c r="A123" s="80"/>
+      <c r="B123" s="5">
+        <v>75</v>
+      </c>
+      <c r="C123" s="58" t="s">
+        <v>269</v>
+      </c>
+      <c r="D123" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" ht="19">
+      <c r="B124" s="72" t="s">
+        <v>225</v>
+      </c>
+      <c r="C124" s="72"/>
+      <c r="D124" s="72"/>
+      <c r="E124" s="72"/>
+      <c r="F124" s="72"/>
+    </row>
+    <row r="125" spans="1:6">
+      <c r="C125" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="D115" s="53" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6">
-      <c r="A116" s="56">
-        <v>38</v>
-      </c>
-      <c r="B116" s="55">
-        <v>70</v>
-      </c>
-      <c r="C116" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="D116" s="53" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6">
-      <c r="A117" s="82" t="s">
-        <v>277</v>
-      </c>
-      <c r="B117" s="55">
-        <v>71</v>
-      </c>
-      <c r="C117" s="76" t="s">
-        <v>216</v>
-      </c>
-      <c r="D117" s="53" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" ht="19">
-      <c r="B118" s="47" t="s">
-        <v>224</v>
-      </c>
-      <c r="C118" s="47"/>
-      <c r="D118" s="47"/>
-      <c r="E118" s="47"/>
-      <c r="F118" s="47"/>
-    </row>
-    <row r="119" spans="1:6">
-      <c r="C119" s="76" t="s">
-        <v>2</v>
-      </c>
-      <c r="D119" s="53" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6">
-      <c r="A120" s="57" t="s">
-        <v>282</v>
-      </c>
-      <c r="B120" s="55">
-        <v>72</v>
-      </c>
-      <c r="C120" s="76" t="s">
-        <v>220</v>
-      </c>
-      <c r="D120" s="53" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6">
-      <c r="A121" s="57"/>
-      <c r="B121" s="55">
-        <v>73</v>
-      </c>
-      <c r="C121" s="76" t="s">
-        <v>221</v>
-      </c>
-      <c r="D121" s="53" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6">
-      <c r="A122" s="57"/>
-      <c r="B122" s="55">
-        <v>74</v>
-      </c>
-      <c r="C122" s="76" t="s">
-        <v>268</v>
-      </c>
-      <c r="D122" s="53" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6">
-      <c r="A123" s="57"/>
-      <c r="B123" s="55">
-        <v>75</v>
-      </c>
-      <c r="C123" s="76" t="s">
-        <v>269</v>
-      </c>
-      <c r="D123" s="53" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" ht="19">
-      <c r="B124" s="47" t="s">
-        <v>225</v>
-      </c>
-      <c r="C124" s="47"/>
-      <c r="D124" s="47"/>
-      <c r="E124" s="47"/>
-      <c r="F124" s="47"/>
-    </row>
-    <row r="125" spans="1:6">
-      <c r="C125" s="76" t="s">
-        <v>2</v>
-      </c>
-      <c r="D125" s="53" t="s">
-        <v>68</v>
+      <c r="D125" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="126" spans="1:6">
-      <c r="A126" s="95" t="s">
+      <c r="A126" s="79" t="s">
         <v>284</v>
       </c>
-      <c r="B126" s="55">
+      <c r="B126" s="5">
         <v>76</v>
       </c>
-      <c r="C126" s="76" t="s">
+      <c r="C126" s="58" t="s">
         <v>226</v>
       </c>
-      <c r="D126" s="53" t="s">
+      <c r="D126" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="A127" s="95"/>
-      <c r="B127" s="55">
+      <c r="A127" s="79"/>
+      <c r="B127" s="5">
         <v>77</v>
       </c>
-      <c r="C127" s="76" t="s">
+      <c r="C127" s="58" t="s">
         <v>227</v>
       </c>
-      <c r="D127" s="53" t="s">
+      <c r="D127" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="128" spans="1:6">
-      <c r="A128" s="95"/>
-      <c r="B128" s="55">
+      <c r="A128" s="79"/>
+      <c r="B128" s="5">
         <v>78</v>
       </c>
-      <c r="C128" s="76" t="s">
+      <c r="C128" s="58" t="s">
         <v>228</v>
       </c>
-      <c r="D128" s="53" t="s">
+      <c r="D128" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="130" spans="3:3">
-      <c r="C130" s="76" t="s">
+      <c r="C130" s="58" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="131" spans="3:3">
-      <c r="C131" s="76" t="s">
+      <c r="C131" s="58" t="s">
         <v>52</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="B46:F46"/>
+    <mergeCell ref="C1:G1"/>
+    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="B9:F9"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="B15:G15"/>
+    <mergeCell ref="B27:G27"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="B35:F35"/>
+    <mergeCell ref="B39:F39"/>
+    <mergeCell ref="B49:F49"/>
+    <mergeCell ref="B52:G52"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B60:F60"/>
+    <mergeCell ref="B67:F67"/>
     <mergeCell ref="A126:A128"/>
     <mergeCell ref="B118:F118"/>
     <mergeCell ref="B124:F124"/>
@@ -6738,23 +6889,7 @@
     <mergeCell ref="B99:F99"/>
     <mergeCell ref="B106:F106"/>
     <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B49:F49"/>
-    <mergeCell ref="B52:G52"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B60:F60"/>
-    <mergeCell ref="B67:F67"/>
     <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B27:G27"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="B35:F35"/>
-    <mergeCell ref="B39:F39"/>
-    <mergeCell ref="B46:F46"/>
-    <mergeCell ref="C1:G1"/>
-    <mergeCell ref="C2:F2"/>
-    <mergeCell ref="B9:F9"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="B15:G15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -6763,17 +6898,316 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8D4C38D-1598-5747-A09D-6C058862D875}">
-  <dimension ref="B1"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="60.5" customWidth="1"/>
+    <col min="2" max="2" width="36.5" customWidth="1"/>
+    <col min="4" max="4" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:2">
+    <row r="1" spans="1:5">
       <c r="B1" s="4"/>
     </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="92" t="s">
+        <v>296</v>
+      </c>
+      <c r="B3" s="92"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="58" t="s">
+        <v>116</v>
+      </c>
+      <c r="B4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C4" s="93" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="58" t="s">
+        <v>118</v>
+      </c>
+      <c r="B5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C5" s="93"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="88" t="s">
+        <v>120</v>
+      </c>
+      <c r="B6" s="89" t="s">
+        <v>121</v>
+      </c>
+      <c r="C6" s="93"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="58" t="s">
+        <v>122</v>
+      </c>
+      <c r="B7" t="s">
+        <v>123</v>
+      </c>
+      <c r="C7" s="93"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="90" t="s">
+        <v>243</v>
+      </c>
+      <c r="B8" s="91" t="s">
+        <v>244</v>
+      </c>
+      <c r="C8" s="93"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="92" t="s">
+        <v>236</v>
+      </c>
+      <c r="B10" s="92"/>
+      <c r="D10" s="92" t="s">
+        <v>302</v>
+      </c>
+      <c r="E10" s="92"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="58" t="s">
+        <v>239</v>
+      </c>
+      <c r="B11" t="s">
+        <v>293</v>
+      </c>
+      <c r="C11" s="93" t="s">
+        <v>236</v>
+      </c>
+      <c r="D11" s="94" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="58" t="s">
+        <v>290</v>
+      </c>
+      <c r="B12" t="s">
+        <v>294</v>
+      </c>
+      <c r="C12" s="93"/>
+      <c r="D12" s="94" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="58" t="s">
+        <v>291</v>
+      </c>
+      <c r="B13" t="s">
+        <v>295</v>
+      </c>
+      <c r="C13" s="93"/>
+      <c r="D13" s="94" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="88" t="s">
+        <v>120</v>
+      </c>
+      <c r="B14" s="89" t="s">
+        <v>121</v>
+      </c>
+      <c r="C14" s="93"/>
+      <c r="D14" s="94" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="90" t="s">
+        <v>243</v>
+      </c>
+      <c r="B15" s="91" t="s">
+        <v>244</v>
+      </c>
+      <c r="C15" s="93"/>
+      <c r="D15" s="94" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="92" t="s">
+        <v>297</v>
+      </c>
+      <c r="B17" s="92"/>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>298</v>
+      </c>
+      <c r="B18" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="92" t="s">
+        <v>236</v>
+      </c>
+      <c r="B21" s="92"/>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
+        <v>300</v>
+      </c>
+      <c r="B22" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
+        <v>301</v>
+      </c>
+      <c r="B23" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="92" t="s">
+        <v>302</v>
+      </c>
+      <c r="B26" s="92"/>
+    </row>
   </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C4:C8"/>
+    <mergeCell ref="C11:C15"/>
+    <mergeCell ref="A21:B21"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38CEFA90-EEC8-C94D-AD41-C862B1E91540}">
+  <dimension ref="A15:F20"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetData>
+    <row r="15" spans="1:6">
+      <c r="A15" s="95" t="s">
+        <v>302</v>
+      </c>
+      <c r="B15" s="96"/>
+      <c r="C15" s="101" t="s">
+        <v>304</v>
+      </c>
+      <c r="D15" s="102"/>
+      <c r="E15" s="109" t="s">
+        <v>305</v>
+      </c>
+      <c r="F15" s="110"/>
+    </row>
+    <row r="16" spans="1:6" ht="16" customHeight="1">
+      <c r="A16" s="97" t="s">
+        <v>306</v>
+      </c>
+      <c r="B16" s="67" t="s">
+        <v>116</v>
+      </c>
+      <c r="C16" s="103" t="s">
+        <v>307</v>
+      </c>
+      <c r="D16" s="104" t="s">
+        <v>116</v>
+      </c>
+      <c r="E16" s="111" t="s">
+        <v>116</v>
+      </c>
+      <c r="F16" s="106"/>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="97" t="s">
+        <v>308</v>
+      </c>
+      <c r="B17" s="67" t="s">
+        <v>118</v>
+      </c>
+      <c r="C17" s="103" t="s">
+        <v>308</v>
+      </c>
+      <c r="D17" s="104" t="s">
+        <v>118</v>
+      </c>
+      <c r="E17" s="105" t="s">
+        <v>118</v>
+      </c>
+      <c r="F17" s="106"/>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="100" t="s">
+        <v>120</v>
+      </c>
+      <c r="B18" s="99"/>
+      <c r="C18" s="105" t="s">
+        <v>120</v>
+      </c>
+      <c r="D18" s="106"/>
+      <c r="E18" s="105" t="s">
+        <v>120</v>
+      </c>
+      <c r="F18" s="106"/>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="97" t="s">
+        <v>311</v>
+      </c>
+      <c r="B19" s="67" t="s">
+        <v>309</v>
+      </c>
+      <c r="C19" s="103" t="s">
+        <v>309</v>
+      </c>
+      <c r="D19" s="104" t="s">
+        <v>122</v>
+      </c>
+      <c r="E19" s="105" t="s">
+        <v>122</v>
+      </c>
+      <c r="F19" s="106"/>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="98" t="s">
+        <v>310</v>
+      </c>
+      <c r="B20" s="70" t="s">
+        <v>292</v>
+      </c>
+      <c r="C20" s="107" t="s">
+        <v>243</v>
+      </c>
+      <c r="D20" s="108"/>
+      <c r="E20" s="107" t="s">
+        <v>243</v>
+      </c>
+      <c r="F20" s="108"/>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="E18:F18"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/docs/Classeur1.xlsx
+++ b/docs/Classeur1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10119"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/artmskfr/Desktop/Formations/3 - GitHub/Projects/2_HealthScope Diabetes/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{024BB04C-03A5-0544-B4F4-F15C0C04E80A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5BE7EAB-4CA8-F849-95F4-A8876C526ACE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="55080" yWindow="-240" windowWidth="29220" windowHeight="20080" activeTab="2" xr2:uid="{36851BB7-FC07-E946-9954-8F3EFDC14535}"/>
+    <workbookView minimized="1" xWindow="60" yWindow="1320" windowWidth="13780" windowHeight="20080" activeTab="5" xr2:uid="{36851BB7-FC07-E946-9954-8F3EFDC14535}"/>
   </bookViews>
   <sheets>
     <sheet name="First ver" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="Third ver" sheetId="4" r:id="rId3"/>
     <sheet name="Alcohol Use" sheetId="2" r:id="rId4"/>
     <sheet name="Feuil1" sheetId="5" r:id="rId5"/>
+    <sheet name="Feuil2" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="928" uniqueCount="320">
   <si>
     <t xml:space="preserve">Examination Data </t>
   </si>
@@ -1344,6 +1345,30 @@
   </si>
   <si>
     <t>ALQ140Q -&gt;</t>
+  </si>
+  <si>
+    <t>RF</t>
+  </si>
+  <si>
+    <t>XGBoost</t>
+  </si>
+  <si>
+    <t>train</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.7444</t>
+  </si>
+  <si>
+    <t>0.7298</t>
+  </si>
+  <si>
+    <t>0.7444</t>
+  </si>
+  <si>
+    <t>0.7402</t>
   </si>
 </sst>
 </file>
@@ -1632,7 +1657,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="112">
+  <cellXfs count="105">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1820,45 +1845,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1869,55 +1855,77 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1926,7 +1934,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2276,13 +2284,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="27">
-      <c r="C1" s="73" t="s">
+      <c r="C1" s="85" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="85"/>
     </row>
     <row r="2" spans="1:7" ht="19">
       <c r="A2" t="s">
@@ -2291,12 +2299,12 @@
       <c r="B2" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="C2" s="72" t="s">
+      <c r="C2" s="83" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="72"/>
-      <c r="E2" s="72"/>
-      <c r="F2" s="72"/>
+      <c r="D2" s="83"/>
+      <c r="E2" s="83"/>
+      <c r="F2" s="83"/>
     </row>
     <row r="3" spans="1:7">
       <c r="B3" s="11">
@@ -2426,16 +2434,16 @@
       <c r="F10" s="9"/>
     </row>
     <row r="11" spans="1:7" ht="19">
-      <c r="B11" s="72" t="s">
+      <c r="B11" s="83" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="72"/>
-      <c r="D11" s="72"/>
-      <c r="E11" s="72"/>
-      <c r="F11" s="72"/>
+      <c r="C11" s="83"/>
+      <c r="D11" s="83"/>
+      <c r="E11" s="83"/>
+      <c r="F11" s="83"/>
     </row>
     <row r="12" spans="1:7" ht="19">
-      <c r="A12" s="77" t="s">
+      <c r="A12" s="81" t="s">
         <v>234</v>
       </c>
       <c r="B12" s="24">
@@ -2451,7 +2459,7 @@
       <c r="F12" s="26"/>
     </row>
     <row r="13" spans="1:7" ht="34" customHeight="1">
-      <c r="A13" s="77"/>
+      <c r="A13" s="81"/>
       <c r="B13" s="27">
         <v>2</v>
       </c>
@@ -2465,12 +2473,12 @@
       <c r="F13" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="G13" s="74" t="s">
+      <c r="G13" s="87" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="34">
-      <c r="A14" s="77"/>
+      <c r="A14" s="81"/>
       <c r="B14" s="27">
         <v>3</v>
       </c>
@@ -2484,10 +2492,10 @@
       <c r="F14" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="G14" s="75"/>
+      <c r="G14" s="88"/>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="77"/>
+      <c r="A15" s="81"/>
       <c r="B15" s="27">
         <v>4</v>
       </c>
@@ -2503,7 +2511,7 @@
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="77"/>
+      <c r="A16" s="81"/>
       <c r="B16" s="27">
         <v>5</v>
       </c>
@@ -2517,14 +2525,14 @@
       <c r="F16" s="25"/>
     </row>
     <row r="17" spans="1:7" ht="27">
-      <c r="B17" s="73" t="s">
+      <c r="B17" s="85" t="s">
         <v>39</v>
       </c>
-      <c r="C17" s="73"/>
-      <c r="D17" s="73"/>
-      <c r="E17" s="73"/>
-      <c r="F17" s="73"/>
-      <c r="G17" s="73"/>
+      <c r="C17" s="85"/>
+      <c r="D17" s="85"/>
+      <c r="E17" s="85"/>
+      <c r="F17" s="85"/>
+      <c r="G17" s="85"/>
     </row>
     <row r="18" spans="1:7" ht="27">
       <c r="B18" s="22"/>
@@ -2675,23 +2683,23 @@
       <c r="F28" s="9"/>
     </row>
     <row r="29" spans="1:7" ht="27">
-      <c r="B29" s="73" t="s">
+      <c r="B29" s="85" t="s">
         <v>60</v>
       </c>
-      <c r="C29" s="73"/>
-      <c r="D29" s="73"/>
-      <c r="E29" s="73"/>
-      <c r="F29" s="73"/>
-      <c r="G29" s="73"/>
+      <c r="C29" s="85"/>
+      <c r="D29" s="85"/>
+      <c r="E29" s="85"/>
+      <c r="F29" s="85"/>
+      <c r="G29" s="85"/>
     </row>
     <row r="30" spans="1:7" ht="19">
-      <c r="B30" s="72" t="s">
+      <c r="B30" s="83" t="s">
         <v>61</v>
       </c>
-      <c r="C30" s="72"/>
-      <c r="D30" s="72"/>
-      <c r="E30" s="72"/>
-      <c r="F30" s="72"/>
+      <c r="C30" s="83"/>
+      <c r="D30" s="83"/>
+      <c r="E30" s="83"/>
+      <c r="F30" s="83"/>
     </row>
     <row r="31" spans="1:7" ht="19">
       <c r="B31" s="24">
@@ -2736,13 +2744,13 @@
       </c>
     </row>
     <row r="34" spans="2:7" ht="19">
-      <c r="B34" s="72" t="s">
+      <c r="B34" s="83" t="s">
         <v>67</v>
       </c>
-      <c r="C34" s="72"/>
-      <c r="D34" s="72"/>
-      <c r="E34" s="72"/>
-      <c r="F34" s="72"/>
+      <c r="C34" s="83"/>
+      <c r="D34" s="83"/>
+      <c r="E34" s="83"/>
+      <c r="F34" s="83"/>
     </row>
     <row r="35" spans="2:7">
       <c r="B35" s="11">
@@ -2771,13 +2779,13 @@
       <c r="F36" s="9"/>
     </row>
     <row r="37" spans="2:7" ht="19">
-      <c r="B37" s="72" t="s">
+      <c r="B37" s="83" t="s">
         <v>71</v>
       </c>
-      <c r="C37" s="72"/>
-      <c r="D37" s="72"/>
-      <c r="E37" s="72"/>
-      <c r="F37" s="72"/>
+      <c r="C37" s="83"/>
+      <c r="D37" s="83"/>
+      <c r="E37" s="83"/>
+      <c r="F37" s="83"/>
     </row>
     <row r="38" spans="2:7">
       <c r="B38" s="34">
@@ -2832,13 +2840,13 @@
       <c r="F41" s="35"/>
     </row>
     <row r="42" spans="2:7" ht="19">
-      <c r="B42" s="71" t="s">
+      <c r="B42" s="86" t="s">
         <v>88</v>
       </c>
-      <c r="C42" s="71"/>
-      <c r="D42" s="71"/>
-      <c r="E42" s="71"/>
-      <c r="F42" s="71"/>
+      <c r="C42" s="86"/>
+      <c r="D42" s="86"/>
+      <c r="E42" s="86"/>
+      <c r="F42" s="86"/>
     </row>
     <row r="43" spans="2:7">
       <c r="B43" s="11"/>
@@ -2952,7 +2960,7 @@
       </c>
     </row>
     <row r="52" spans="1:7">
-      <c r="A52" s="78" t="s">
+      <c r="A52" s="82" t="s">
         <v>235</v>
       </c>
       <c r="B52" s="11"/>
@@ -2969,7 +2977,7 @@
       </c>
     </row>
     <row r="53" spans="1:7">
-      <c r="A53" s="78"/>
+      <c r="A53" s="82"/>
       <c r="B53" s="11"/>
       <c r="C53" s="9" t="s">
         <v>101</v>
@@ -2984,13 +2992,13 @@
       </c>
     </row>
     <row r="54" spans="1:7" ht="19">
-      <c r="B54" s="72" t="s">
+      <c r="B54" s="83" t="s">
         <v>104</v>
       </c>
-      <c r="C54" s="72"/>
-      <c r="D54" s="72"/>
-      <c r="E54" s="72"/>
-      <c r="F54" s="72"/>
+      <c r="C54" s="83"/>
+      <c r="D54" s="83"/>
+      <c r="E54" s="83"/>
+      <c r="F54" s="83"/>
     </row>
     <row r="55" spans="1:7">
       <c r="C55" t="s">
@@ -3012,13 +3020,13 @@
       </c>
     </row>
     <row r="57" spans="1:7" ht="19">
-      <c r="B57" s="72" t="s">
+      <c r="B57" s="83" t="s">
         <v>108</v>
       </c>
-      <c r="C57" s="72"/>
-      <c r="D57" s="72"/>
-      <c r="E57" s="72"/>
-      <c r="F57" s="72"/>
+      <c r="C57" s="83"/>
+      <c r="D57" s="83"/>
+      <c r="E57" s="83"/>
+      <c r="F57" s="83"/>
     </row>
     <row r="58" spans="1:7">
       <c r="C58" t="s">
@@ -3048,23 +3056,23 @@
       </c>
     </row>
     <row r="61" spans="1:7" ht="27">
-      <c r="B61" s="73" t="s">
+      <c r="B61" s="85" t="s">
         <v>114</v>
       </c>
-      <c r="C61" s="73"/>
-      <c r="D61" s="73"/>
-      <c r="E61" s="73"/>
-      <c r="F61" s="73"/>
-      <c r="G61" s="73"/>
+      <c r="C61" s="85"/>
+      <c r="D61" s="85"/>
+      <c r="E61" s="85"/>
+      <c r="F61" s="85"/>
+      <c r="G61" s="85"/>
     </row>
     <row r="62" spans="1:7" ht="19">
-      <c r="B62" s="72" t="s">
+      <c r="B62" s="83" t="s">
         <v>115</v>
       </c>
-      <c r="C62" s="72"/>
-      <c r="D62" s="72"/>
-      <c r="E62" s="72"/>
-      <c r="F62" s="72"/>
+      <c r="C62" s="83"/>
+      <c r="D62" s="83"/>
+      <c r="E62" s="83"/>
+      <c r="F62" s="83"/>
     </row>
     <row r="63" spans="1:7">
       <c r="C63" t="s">
@@ -3136,13 +3144,13 @@
       </c>
     </row>
     <row r="69" spans="1:6" ht="19">
-      <c r="B69" s="72" t="s">
+      <c r="B69" s="83" t="s">
         <v>128</v>
       </c>
-      <c r="C69" s="72"/>
-      <c r="D69" s="72"/>
-      <c r="E69" s="72"/>
-      <c r="F69" s="72"/>
+      <c r="C69" s="83"/>
+      <c r="D69" s="83"/>
+      <c r="E69" s="83"/>
+      <c r="F69" s="83"/>
     </row>
     <row r="70" spans="1:6">
       <c r="C70" t="s">
@@ -3211,13 +3219,13 @@
       </c>
     </row>
     <row r="76" spans="1:6" ht="19">
-      <c r="B76" s="72" t="s">
+      <c r="B76" s="83" t="s">
         <v>142</v>
       </c>
-      <c r="C76" s="72"/>
-      <c r="D76" s="72"/>
-      <c r="E76" s="72"/>
-      <c r="F76" s="72"/>
+      <c r="C76" s="83"/>
+      <c r="D76" s="83"/>
+      <c r="E76" s="83"/>
+      <c r="F76" s="83"/>
     </row>
     <row r="77" spans="1:6">
       <c r="C77" t="s">
@@ -3247,13 +3255,13 @@
       </c>
     </row>
     <row r="80" spans="1:6" ht="19">
-      <c r="B80" s="72" t="s">
+      <c r="B80" s="83" t="s">
         <v>147</v>
       </c>
-      <c r="C80" s="72"/>
-      <c r="D80" s="72"/>
-      <c r="E80" s="72"/>
-      <c r="F80" s="72"/>
+      <c r="C80" s="83"/>
+      <c r="D80" s="83"/>
+      <c r="E80" s="83"/>
+      <c r="F80" s="83"/>
     </row>
     <row r="81" spans="2:7">
       <c r="C81" t="s">
@@ -3264,7 +3272,7 @@
       </c>
     </row>
     <row r="82" spans="2:7">
-      <c r="B82" s="76" t="s">
+      <c r="B82" s="84" t="s">
         <v>232</v>
       </c>
       <c r="C82" t="s">
@@ -3281,7 +3289,7 @@
       </c>
     </row>
     <row r="83" spans="2:7">
-      <c r="B83" s="76"/>
+      <c r="B83" s="84"/>
       <c r="C83" t="s">
         <v>152</v>
       </c>
@@ -3290,7 +3298,7 @@
       </c>
     </row>
     <row r="84" spans="2:7">
-      <c r="B84" s="76"/>
+      <c r="B84" s="84"/>
       <c r="C84" t="s">
         <v>154</v>
       </c>
@@ -3299,7 +3307,7 @@
       </c>
     </row>
     <row r="85" spans="2:7">
-      <c r="B85" s="76"/>
+      <c r="B85" s="84"/>
       <c r="C85" t="s">
         <v>156</v>
       </c>
@@ -3308,7 +3316,7 @@
       </c>
     </row>
     <row r="86" spans="2:7">
-      <c r="B86" s="76"/>
+      <c r="B86" s="84"/>
       <c r="C86" t="s">
         <v>158</v>
       </c>
@@ -3317,13 +3325,13 @@
       </c>
     </row>
     <row r="87" spans="2:7" ht="19">
-      <c r="B87" s="72" t="s">
+      <c r="B87" s="83" t="s">
         <v>160</v>
       </c>
-      <c r="C87" s="72"/>
-      <c r="D87" s="72"/>
-      <c r="E87" s="72"/>
-      <c r="F87" s="72"/>
+      <c r="C87" s="83"/>
+      <c r="D87" s="83"/>
+      <c r="E87" s="83"/>
+      <c r="F87" s="83"/>
     </row>
     <row r="88" spans="2:7">
       <c r="C88" t="s">
@@ -3345,13 +3353,13 @@
       </c>
     </row>
     <row r="90" spans="2:7" ht="19">
-      <c r="B90" s="72" t="s">
+      <c r="B90" s="83" t="s">
         <v>164</v>
       </c>
-      <c r="C90" s="72"/>
-      <c r="D90" s="72"/>
-      <c r="E90" s="72"/>
-      <c r="F90" s="72"/>
+      <c r="C90" s="83"/>
+      <c r="D90" s="83"/>
+      <c r="E90" s="83"/>
+      <c r="F90" s="83"/>
     </row>
     <row r="91" spans="2:7">
       <c r="C91" t="s">
@@ -3384,13 +3392,13 @@
       </c>
     </row>
     <row r="94" spans="2:7" ht="19">
-      <c r="B94" s="72" t="s">
+      <c r="B94" s="83" t="s">
         <v>171</v>
       </c>
-      <c r="C94" s="72"/>
-      <c r="D94" s="72"/>
-      <c r="E94" s="72"/>
-      <c r="F94" s="72"/>
+      <c r="C94" s="83"/>
+      <c r="D94" s="83"/>
+      <c r="E94" s="83"/>
+      <c r="F94" s="83"/>
     </row>
     <row r="95" spans="2:7">
       <c r="C95" t="s">
@@ -3473,13 +3481,13 @@
       </c>
     </row>
     <row r="103" spans="1:6" ht="19">
-      <c r="B103" s="72" t="s">
+      <c r="B103" s="83" t="s">
         <v>187</v>
       </c>
-      <c r="C103" s="72"/>
-      <c r="D103" s="72"/>
-      <c r="E103" s="72"/>
-      <c r="F103" s="72"/>
+      <c r="C103" s="83"/>
+      <c r="D103" s="83"/>
+      <c r="E103" s="83"/>
+      <c r="F103" s="83"/>
     </row>
     <row r="104" spans="1:6">
       <c r="C104" t="s">
@@ -3530,13 +3538,13 @@
       </c>
     </row>
     <row r="110" spans="1:6" ht="19">
-      <c r="B110" s="72" t="s">
+      <c r="B110" s="83" t="s">
         <v>198</v>
       </c>
-      <c r="C110" s="72"/>
-      <c r="D110" s="72"/>
-      <c r="E110" s="72"/>
-      <c r="F110" s="72"/>
+      <c r="C110" s="83"/>
+      <c r="D110" s="83"/>
+      <c r="E110" s="83"/>
+      <c r="F110" s="83"/>
     </row>
     <row r="111" spans="1:6">
       <c r="C111" t="s">
@@ -3547,7 +3555,7 @@
       </c>
     </row>
     <row r="112" spans="1:6">
-      <c r="B112" s="76" t="s">
+      <c r="B112" s="84" t="s">
         <v>233</v>
       </c>
       <c r="C112" t="s">
@@ -3558,7 +3566,7 @@
       </c>
     </row>
     <row r="113" spans="1:6">
-      <c r="B113" s="76"/>
+      <c r="B113" s="84"/>
       <c r="C113" t="s">
         <v>201</v>
       </c>
@@ -3567,7 +3575,7 @@
       </c>
     </row>
     <row r="114" spans="1:6">
-      <c r="B114" s="76"/>
+      <c r="B114" s="84"/>
       <c r="C114" t="s">
         <v>203</v>
       </c>
@@ -3576,7 +3584,7 @@
       </c>
     </row>
     <row r="115" spans="1:6">
-      <c r="B115" s="76"/>
+      <c r="B115" s="84"/>
       <c r="C115" t="s">
         <v>205</v>
       </c>
@@ -3588,7 +3596,7 @@
       </c>
     </row>
     <row r="116" spans="1:6">
-      <c r="B116" s="76"/>
+      <c r="B116" s="84"/>
       <c r="C116" t="s">
         <v>207</v>
       </c>
@@ -3608,13 +3616,13 @@
       </c>
     </row>
     <row r="118" spans="1:6" ht="19">
-      <c r="B118" s="72" t="s">
+      <c r="B118" s="83" t="s">
         <v>213</v>
       </c>
-      <c r="C118" s="72"/>
-      <c r="D118" s="72"/>
-      <c r="E118" s="72"/>
-      <c r="F118" s="72"/>
+      <c r="C118" s="83"/>
+      <c r="D118" s="83"/>
+      <c r="E118" s="83"/>
+      <c r="F118" s="83"/>
     </row>
     <row r="119" spans="1:6">
       <c r="C119" t="s">
@@ -3655,13 +3663,13 @@
       </c>
     </row>
     <row r="123" spans="1:6" ht="19">
-      <c r="B123" s="72" t="s">
+      <c r="B123" s="83" t="s">
         <v>224</v>
       </c>
-      <c r="C123" s="72"/>
-      <c r="D123" s="72"/>
-      <c r="E123" s="72"/>
-      <c r="F123" s="72"/>
+      <c r="C123" s="83"/>
+      <c r="D123" s="83"/>
+      <c r="E123" s="83"/>
+      <c r="F123" s="83"/>
     </row>
     <row r="124" spans="1:6">
       <c r="C124" t="s">
@@ -3688,13 +3696,13 @@
       </c>
     </row>
     <row r="127" spans="1:6" ht="19">
-      <c r="B127" s="72" t="s">
+      <c r="B127" s="83" t="s">
         <v>225</v>
       </c>
-      <c r="C127" s="72"/>
-      <c r="D127" s="72"/>
-      <c r="E127" s="72"/>
-      <c r="F127" s="72"/>
+      <c r="C127" s="83"/>
+      <c r="D127" s="83"/>
+      <c r="E127" s="83"/>
+      <c r="F127" s="83"/>
     </row>
     <row r="128" spans="1:6">
       <c r="C128" t="s">
@@ -3705,7 +3713,7 @@
       </c>
     </row>
     <row r="129" spans="2:4">
-      <c r="B129" s="76" t="s">
+      <c r="B129" s="84" t="s">
         <v>232</v>
       </c>
       <c r="C129" t="s">
@@ -3716,7 +3724,7 @@
       </c>
     </row>
     <row r="130" spans="2:4">
-      <c r="B130" s="76"/>
+      <c r="B130" s="84"/>
       <c r="C130" t="s">
         <v>227</v>
       </c>
@@ -3725,7 +3733,7 @@
       </c>
     </row>
     <row r="131" spans="2:4">
-      <c r="B131" s="76"/>
+      <c r="B131" s="84"/>
       <c r="C131" t="s">
         <v>228</v>
       </c>
@@ -3735,6 +3743,20 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="B42:F42"/>
+    <mergeCell ref="B54:F54"/>
+    <mergeCell ref="C1:G1"/>
+    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="B17:G17"/>
+    <mergeCell ref="B129:B131"/>
+    <mergeCell ref="B87:F87"/>
+    <mergeCell ref="B90:F90"/>
+    <mergeCell ref="B94:F94"/>
+    <mergeCell ref="B103:F103"/>
+    <mergeCell ref="B110:F110"/>
+    <mergeCell ref="B118:F118"/>
     <mergeCell ref="A12:A16"/>
     <mergeCell ref="A52:A53"/>
     <mergeCell ref="B123:F123"/>
@@ -3751,20 +3773,6 @@
     <mergeCell ref="B30:F30"/>
     <mergeCell ref="B34:F34"/>
     <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B129:B131"/>
-    <mergeCell ref="B87:F87"/>
-    <mergeCell ref="B90:F90"/>
-    <mergeCell ref="B94:F94"/>
-    <mergeCell ref="B103:F103"/>
-    <mergeCell ref="B110:F110"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B42:F42"/>
-    <mergeCell ref="B54:F54"/>
-    <mergeCell ref="C1:G1"/>
-    <mergeCell ref="C2:F2"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="G13:G14"/>
-    <mergeCell ref="B17:G17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -3786,24 +3794,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="27">
-      <c r="C1" s="73" t="s">
+      <c r="C1" s="85" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="85"/>
     </row>
     <row r="2" spans="1:7" ht="19">
       <c r="A2" t="s">
         <v>236</v>
       </c>
-      <c r="C2" s="72" t="s">
+      <c r="C2" s="83" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="72"/>
-      <c r="E2" s="72"/>
-      <c r="F2" s="72"/>
+      <c r="D2" s="83"/>
+      <c r="E2" s="83"/>
+      <c r="F2" s="83"/>
     </row>
     <row r="3" spans="1:7">
       <c r="B3" s="11">
@@ -3900,16 +3908,16 @@
       </c>
     </row>
     <row r="9" spans="1:7" ht="19">
-      <c r="B9" s="72" t="s">
+      <c r="B9" s="83" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="72"/>
-      <c r="D9" s="72"/>
-      <c r="E9" s="72"/>
-      <c r="F9" s="72"/>
+      <c r="C9" s="83"/>
+      <c r="D9" s="83"/>
+      <c r="E9" s="83"/>
+      <c r="F9" s="83"/>
     </row>
     <row r="10" spans="1:7" ht="19">
-      <c r="A10" s="77" t="s">
+      <c r="A10" s="81" t="s">
         <v>234</v>
       </c>
       <c r="B10" s="24"/>
@@ -3923,7 +3931,7 @@
       <c r="F10" s="26"/>
     </row>
     <row r="11" spans="1:7" ht="34" customHeight="1">
-      <c r="A11" s="77"/>
+      <c r="A11" s="81"/>
       <c r="B11" s="27">
         <v>9</v>
       </c>
@@ -3937,12 +3945,12 @@
       <c r="F11" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="G11" s="74" t="s">
+      <c r="G11" s="87" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="34">
-      <c r="A12" s="77"/>
+      <c r="A12" s="81"/>
       <c r="B12" s="27">
         <v>10</v>
       </c>
@@ -3956,10 +3964,10 @@
       <c r="F12" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="G12" s="75"/>
+      <c r="G12" s="88"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="77"/>
+      <c r="A13" s="81"/>
       <c r="B13" s="27">
         <v>11</v>
       </c>
@@ -3975,7 +3983,7 @@
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="77"/>
+      <c r="A14" s="81"/>
       <c r="B14" s="27">
         <v>12</v>
       </c>
@@ -3989,14 +3997,14 @@
       <c r="F14" s="25"/>
     </row>
     <row r="15" spans="1:7" ht="27">
-      <c r="B15" s="73" t="s">
+      <c r="B15" s="85" t="s">
         <v>39</v>
       </c>
-      <c r="C15" s="73"/>
-      <c r="D15" s="73"/>
-      <c r="E15" s="73"/>
-      <c r="F15" s="73"/>
-      <c r="G15" s="73"/>
+      <c r="C15" s="85"/>
+      <c r="D15" s="85"/>
+      <c r="E15" s="85"/>
+      <c r="F15" s="85"/>
+      <c r="G15" s="85"/>
     </row>
     <row r="16" spans="1:7" ht="27">
       <c r="B16" s="22"/>
@@ -4147,23 +4155,23 @@
       <c r="F26" s="9"/>
     </row>
     <row r="27" spans="1:7" ht="27">
-      <c r="B27" s="73" t="s">
+      <c r="B27" s="85" t="s">
         <v>60</v>
       </c>
-      <c r="C27" s="73"/>
-      <c r="D27" s="73"/>
-      <c r="E27" s="73"/>
-      <c r="F27" s="73"/>
-      <c r="G27" s="73"/>
+      <c r="C27" s="85"/>
+      <c r="D27" s="85"/>
+      <c r="E27" s="85"/>
+      <c r="F27" s="85"/>
+      <c r="G27" s="85"/>
     </row>
     <row r="28" spans="1:7" ht="19">
-      <c r="B28" s="72" t="s">
+      <c r="B28" s="83" t="s">
         <v>61</v>
       </c>
-      <c r="C28" s="72"/>
-      <c r="D28" s="72"/>
-      <c r="E28" s="72"/>
-      <c r="F28" s="72"/>
+      <c r="C28" s="83"/>
+      <c r="D28" s="83"/>
+      <c r="E28" s="83"/>
+      <c r="F28" s="83"/>
     </row>
     <row r="29" spans="1:7" ht="19">
       <c r="B29" s="43"/>
@@ -4206,13 +4214,13 @@
       </c>
     </row>
     <row r="32" spans="1:7" ht="19">
-      <c r="B32" s="72" t="s">
+      <c r="B32" s="83" t="s">
         <v>67</v>
       </c>
-      <c r="C32" s="72"/>
-      <c r="D32" s="72"/>
-      <c r="E32" s="72"/>
-      <c r="F32" s="72"/>
+      <c r="C32" s="83"/>
+      <c r="D32" s="83"/>
+      <c r="E32" s="83"/>
+      <c r="F32" s="83"/>
     </row>
     <row r="33" spans="2:7">
       <c r="B33" s="11"/>
@@ -4239,13 +4247,13 @@
       <c r="F34" s="9"/>
     </row>
     <row r="35" spans="2:7" ht="19">
-      <c r="B35" s="72" t="s">
+      <c r="B35" s="83" t="s">
         <v>71</v>
       </c>
-      <c r="C35" s="72"/>
-      <c r="D35" s="72"/>
-      <c r="E35" s="72"/>
-      <c r="F35" s="72"/>
+      <c r="C35" s="83"/>
+      <c r="D35" s="83"/>
+      <c r="E35" s="83"/>
+      <c r="F35" s="83"/>
     </row>
     <row r="36" spans="2:7">
       <c r="B36" s="34"/>
@@ -4283,13 +4291,13 @@
       <c r="F38" s="35"/>
     </row>
     <row r="39" spans="2:7" ht="19">
-      <c r="B39" s="71" t="s">
+      <c r="B39" s="86" t="s">
         <v>88</v>
       </c>
-      <c r="C39" s="71"/>
-      <c r="D39" s="71"/>
-      <c r="E39" s="71"/>
-      <c r="F39" s="71"/>
+      <c r="C39" s="86"/>
+      <c r="D39" s="86"/>
+      <c r="E39" s="86"/>
+      <c r="F39" s="86"/>
     </row>
     <row r="40" spans="2:7">
       <c r="B40" s="11"/>
@@ -4378,13 +4386,13 @@
       </c>
     </row>
     <row r="46" spans="2:7" ht="19">
-      <c r="B46" s="72" t="s">
+      <c r="B46" s="83" t="s">
         <v>104</v>
       </c>
-      <c r="C46" s="72"/>
-      <c r="D46" s="72"/>
-      <c r="E46" s="72"/>
-      <c r="F46" s="72"/>
+      <c r="C46" s="83"/>
+      <c r="D46" s="83"/>
+      <c r="E46" s="83"/>
+      <c r="F46" s="83"/>
     </row>
     <row r="47" spans="2:7">
       <c r="C47" t="s">
@@ -4409,13 +4417,13 @@
       </c>
     </row>
     <row r="49" spans="1:7" ht="19">
-      <c r="B49" s="72" t="s">
+      <c r="B49" s="83" t="s">
         <v>108</v>
       </c>
-      <c r="C49" s="72"/>
-      <c r="D49" s="72"/>
-      <c r="E49" s="72"/>
-      <c r="F49" s="72"/>
+      <c r="C49" s="83"/>
+      <c r="D49" s="83"/>
+      <c r="E49" s="83"/>
+      <c r="F49" s="83"/>
     </row>
     <row r="50" spans="1:7">
       <c r="C50" t="s">
@@ -4440,23 +4448,23 @@
       </c>
     </row>
     <row r="52" spans="1:7" ht="27">
-      <c r="B52" s="73" t="s">
+      <c r="B52" s="85" t="s">
         <v>114</v>
       </c>
-      <c r="C52" s="73"/>
-      <c r="D52" s="73"/>
-      <c r="E52" s="73"/>
-      <c r="F52" s="73"/>
-      <c r="G52" s="73"/>
+      <c r="C52" s="85"/>
+      <c r="D52" s="85"/>
+      <c r="E52" s="85"/>
+      <c r="F52" s="85"/>
+      <c r="G52" s="85"/>
     </row>
     <row r="53" spans="1:7" ht="19">
-      <c r="B53" s="72" t="s">
+      <c r="B53" s="83" t="s">
         <v>115</v>
       </c>
-      <c r="C53" s="72"/>
-      <c r="D53" s="72"/>
-      <c r="E53" s="72"/>
-      <c r="F53" s="72"/>
+      <c r="C53" s="83"/>
+      <c r="D53" s="83"/>
+      <c r="E53" s="83"/>
+      <c r="F53" s="83"/>
     </row>
     <row r="54" spans="1:7">
       <c r="C54" t="s">
@@ -4543,13 +4551,13 @@
       </c>
     </row>
     <row r="60" spans="1:7" ht="19">
-      <c r="B60" s="72" t="s">
+      <c r="B60" s="83" t="s">
         <v>128</v>
       </c>
-      <c r="C60" s="72"/>
-      <c r="D60" s="72"/>
-      <c r="E60" s="72"/>
-      <c r="F60" s="72"/>
+      <c r="C60" s="83"/>
+      <c r="D60" s="83"/>
+      <c r="E60" s="83"/>
+      <c r="F60" s="83"/>
     </row>
     <row r="61" spans="1:7">
       <c r="C61" t="s">
@@ -4624,13 +4632,13 @@
       </c>
     </row>
     <row r="67" spans="2:7" ht="19">
-      <c r="B67" s="72" t="s">
+      <c r="B67" s="83" t="s">
         <v>142</v>
       </c>
-      <c r="C67" s="72"/>
-      <c r="D67" s="72"/>
-      <c r="E67" s="72"/>
-      <c r="F67" s="72"/>
+      <c r="C67" s="83"/>
+      <c r="D67" s="83"/>
+      <c r="E67" s="83"/>
+      <c r="F67" s="83"/>
     </row>
     <row r="68" spans="2:7">
       <c r="C68" t="s">
@@ -4679,13 +4687,13 @@
       </c>
     </row>
     <row r="73" spans="2:7" ht="19">
-      <c r="B73" s="72" t="s">
+      <c r="B73" s="83" t="s">
         <v>147</v>
       </c>
-      <c r="C73" s="72"/>
-      <c r="D73" s="72"/>
-      <c r="E73" s="72"/>
-      <c r="F73" s="72"/>
+      <c r="C73" s="83"/>
+      <c r="D73" s="83"/>
+      <c r="E73" s="83"/>
+      <c r="F73" s="83"/>
     </row>
     <row r="74" spans="2:7">
       <c r="C74" t="s">
@@ -4789,13 +4797,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="19">
-      <c r="B85" s="72" t="s">
+      <c r="B85" s="83" t="s">
         <v>160</v>
       </c>
-      <c r="C85" s="72"/>
-      <c r="D85" s="72"/>
-      <c r="E85" s="72"/>
-      <c r="F85" s="72"/>
+      <c r="C85" s="83"/>
+      <c r="D85" s="83"/>
+      <c r="E85" s="83"/>
+      <c r="F85" s="83"/>
     </row>
     <row r="86" spans="2:6">
       <c r="C86" t="s">
@@ -4820,13 +4828,13 @@
       </c>
     </row>
     <row r="88" spans="2:6" ht="19">
-      <c r="B88" s="72" t="s">
+      <c r="B88" s="83" t="s">
         <v>164</v>
       </c>
-      <c r="C88" s="72"/>
-      <c r="D88" s="72"/>
-      <c r="E88" s="72"/>
-      <c r="F88" s="72"/>
+      <c r="C88" s="83"/>
+      <c r="D88" s="83"/>
+      <c r="E88" s="83"/>
+      <c r="F88" s="83"/>
     </row>
     <row r="89" spans="2:6">
       <c r="C89" t="s">
@@ -4862,13 +4870,13 @@
       </c>
     </row>
     <row r="92" spans="2:6" ht="19">
-      <c r="B92" s="72" t="s">
+      <c r="B92" s="83" t="s">
         <v>171</v>
       </c>
-      <c r="C92" s="72"/>
-      <c r="D92" s="72"/>
-      <c r="E92" s="72"/>
-      <c r="F92" s="72"/>
+      <c r="C92" s="83"/>
+      <c r="D92" s="83"/>
+      <c r="E92" s="83"/>
+      <c r="F92" s="83"/>
     </row>
     <row r="93" spans="2:6">
       <c r="C93" t="s">
@@ -4934,13 +4942,13 @@
       </c>
     </row>
     <row r="99" spans="2:6" ht="19">
-      <c r="B99" s="72" t="s">
+      <c r="B99" s="83" t="s">
         <v>187</v>
       </c>
-      <c r="C99" s="72"/>
-      <c r="D99" s="72"/>
-      <c r="E99" s="72"/>
-      <c r="F99" s="72"/>
+      <c r="C99" s="83"/>
+      <c r="D99" s="83"/>
+      <c r="E99" s="83"/>
+      <c r="F99" s="83"/>
     </row>
     <row r="100" spans="2:6">
       <c r="C100" t="s">
@@ -5006,13 +5014,13 @@
       </c>
     </row>
     <row r="106" spans="2:6" ht="19">
-      <c r="B106" s="72" t="s">
+      <c r="B106" s="83" t="s">
         <v>198</v>
       </c>
-      <c r="C106" s="72"/>
-      <c r="D106" s="72"/>
-      <c r="E106" s="72"/>
-      <c r="F106" s="72"/>
+      <c r="C106" s="83"/>
+      <c r="D106" s="83"/>
+      <c r="E106" s="83"/>
+      <c r="F106" s="83"/>
     </row>
     <row r="107" spans="2:6">
       <c r="C107" t="s">
@@ -5095,13 +5103,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="19">
-      <c r="B114" s="72" t="s">
+      <c r="B114" s="83" t="s">
         <v>213</v>
       </c>
-      <c r="C114" s="72"/>
-      <c r="D114" s="72"/>
-      <c r="E114" s="72"/>
-      <c r="F114" s="72"/>
+      <c r="C114" s="83"/>
+      <c r="D114" s="83"/>
+      <c r="E114" s="83"/>
+      <c r="F114" s="83"/>
     </row>
     <row r="115" spans="2:6">
       <c r="C115" t="s">
@@ -5134,13 +5142,13 @@
       </c>
     </row>
     <row r="118" spans="2:6" ht="19">
-      <c r="B118" s="72" t="s">
+      <c r="B118" s="83" t="s">
         <v>224</v>
       </c>
-      <c r="C118" s="72"/>
-      <c r="D118" s="72"/>
-      <c r="E118" s="72"/>
-      <c r="F118" s="72"/>
+      <c r="C118" s="83"/>
+      <c r="D118" s="83"/>
+      <c r="E118" s="83"/>
+      <c r="F118" s="83"/>
     </row>
     <row r="119" spans="2:6">
       <c r="C119" t="s">
@@ -5189,13 +5197,13 @@
       </c>
     </row>
     <row r="124" spans="2:6" ht="19">
-      <c r="B124" s="72" t="s">
+      <c r="B124" s="83" t="s">
         <v>225</v>
       </c>
-      <c r="C124" s="72"/>
-      <c r="D124" s="72"/>
-      <c r="E124" s="72"/>
-      <c r="F124" s="72"/>
+      <c r="C124" s="83"/>
+      <c r="D124" s="83"/>
+      <c r="E124" s="83"/>
+      <c r="F124" s="83"/>
     </row>
     <row r="125" spans="2:6">
       <c r="C125" t="s">
@@ -5240,15 +5248,12 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="B106:F106"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B88:F88"/>
-    <mergeCell ref="B92:F92"/>
-    <mergeCell ref="B99:F99"/>
+    <mergeCell ref="B15:G15"/>
+    <mergeCell ref="C1:G1"/>
+    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="B9:F9"/>
+    <mergeCell ref="A10:A14"/>
+    <mergeCell ref="G11:G12"/>
     <mergeCell ref="B67:F67"/>
     <mergeCell ref="B27:G27"/>
     <mergeCell ref="B28:F28"/>
@@ -5260,12 +5265,15 @@
     <mergeCell ref="B52:G52"/>
     <mergeCell ref="B53:F53"/>
     <mergeCell ref="B60:F60"/>
-    <mergeCell ref="B15:G15"/>
-    <mergeCell ref="C1:G1"/>
-    <mergeCell ref="C2:F2"/>
-    <mergeCell ref="B9:F9"/>
-    <mergeCell ref="A10:A14"/>
-    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="B106:F106"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B88:F88"/>
+    <mergeCell ref="B92:F92"/>
+    <mergeCell ref="B99:F99"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -5287,13 +5295,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="27">
-      <c r="C1" s="73" t="s">
+      <c r="C1" s="85" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="85"/>
     </row>
     <row r="2" spans="1:7" ht="19">
       <c r="A2" s="62" t="s">
@@ -5302,12 +5310,12 @@
       <c r="B2" s="62" t="s">
         <v>274</v>
       </c>
-      <c r="C2" s="72" t="s">
+      <c r="C2" s="83" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="72"/>
-      <c r="E2" s="72"/>
-      <c r="F2" s="72"/>
+      <c r="D2" s="83"/>
+      <c r="E2" s="83"/>
+      <c r="F2" s="83"/>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="1">
@@ -5418,13 +5426,13 @@
       </c>
     </row>
     <row r="9" spans="1:7" ht="19">
-      <c r="B9" s="72" t="s">
+      <c r="B9" s="83" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="72"/>
-      <c r="D9" s="72"/>
-      <c r="E9" s="72"/>
-      <c r="F9" s="72"/>
+      <c r="C9" s="83"/>
+      <c r="D9" s="83"/>
+      <c r="E9" s="83"/>
+      <c r="F9" s="83"/>
     </row>
     <row r="10" spans="1:7" ht="19">
       <c r="A10" s="46"/>
@@ -5454,7 +5462,7 @@
       <c r="F11" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="G11" s="74" t="s">
+      <c r="G11" s="87" t="s">
         <v>34</v>
       </c>
     </row>
@@ -5474,7 +5482,7 @@
       <c r="F12" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="G12" s="75"/>
+      <c r="G12" s="88"/>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="46">
@@ -5506,14 +5514,14 @@
       </c>
     </row>
     <row r="15" spans="1:7" ht="27">
-      <c r="B15" s="73" t="s">
+      <c r="B15" s="85" t="s">
         <v>39</v>
       </c>
-      <c r="C15" s="73"/>
-      <c r="D15" s="73"/>
-      <c r="E15" s="73"/>
-      <c r="F15" s="73"/>
-      <c r="G15" s="73"/>
+      <c r="C15" s="85"/>
+      <c r="D15" s="85"/>
+      <c r="E15" s="85"/>
+      <c r="F15" s="85"/>
+      <c r="G15" s="85"/>
     </row>
     <row r="16" spans="1:7" ht="27">
       <c r="B16" s="49"/>
@@ -5654,23 +5662,23 @@
       </c>
     </row>
     <row r="27" spans="1:7" ht="27">
-      <c r="B27" s="73" t="s">
+      <c r="B27" s="85" t="s">
         <v>60</v>
       </c>
-      <c r="C27" s="73"/>
-      <c r="D27" s="73"/>
-      <c r="E27" s="73"/>
-      <c r="F27" s="73"/>
-      <c r="G27" s="73"/>
+      <c r="C27" s="85"/>
+      <c r="D27" s="85"/>
+      <c r="E27" s="85"/>
+      <c r="F27" s="85"/>
+      <c r="G27" s="85"/>
     </row>
     <row r="28" spans="1:7" ht="19">
-      <c r="B28" s="72" t="s">
+      <c r="B28" s="83" t="s">
         <v>61</v>
       </c>
-      <c r="C28" s="72"/>
-      <c r="D28" s="72"/>
-      <c r="E28" s="72"/>
-      <c r="F28" s="72"/>
+      <c r="C28" s="83"/>
+      <c r="D28" s="83"/>
+      <c r="E28" s="83"/>
+      <c r="F28" s="83"/>
     </row>
     <row r="29" spans="1:7" ht="19">
       <c r="B29" s="50"/>
@@ -5709,13 +5717,13 @@
       </c>
     </row>
     <row r="32" spans="1:7" ht="19">
-      <c r="B32" s="72" t="s">
+      <c r="B32" s="83" t="s">
         <v>67</v>
       </c>
-      <c r="C32" s="72"/>
-      <c r="D32" s="72"/>
-      <c r="E32" s="72"/>
-      <c r="F32" s="72"/>
+      <c r="C32" s="83"/>
+      <c r="D32" s="83"/>
+      <c r="E32" s="83"/>
+      <c r="F32" s="83"/>
     </row>
     <row r="33" spans="1:7">
       <c r="C33" s="58" t="s">
@@ -5740,13 +5748,13 @@
       </c>
     </row>
     <row r="35" spans="1:7" ht="19">
-      <c r="B35" s="72" t="s">
+      <c r="B35" s="83" t="s">
         <v>71</v>
       </c>
-      <c r="C35" s="72"/>
-      <c r="D35" s="72"/>
-      <c r="E35" s="72"/>
-      <c r="F35" s="72"/>
+      <c r="C35" s="83"/>
+      <c r="D35" s="83"/>
+      <c r="E35" s="83"/>
+      <c r="F35" s="83"/>
     </row>
     <row r="36" spans="1:7">
       <c r="C36" s="58" t="s">
@@ -5779,13 +5787,13 @@
       </c>
     </row>
     <row r="39" spans="1:7" ht="19">
-      <c r="B39" s="71" t="s">
+      <c r="B39" s="86" t="s">
         <v>88</v>
       </c>
-      <c r="C39" s="71"/>
-      <c r="D39" s="71"/>
-      <c r="E39" s="71"/>
-      <c r="F39" s="71"/>
+      <c r="C39" s="86"/>
+      <c r="D39" s="86"/>
+      <c r="E39" s="86"/>
+      <c r="F39" s="86"/>
     </row>
     <row r="40" spans="1:7">
       <c r="C40" s="58" t="s">
@@ -5878,13 +5886,13 @@
       </c>
     </row>
     <row r="46" spans="1:7" ht="19">
-      <c r="B46" s="72" t="s">
+      <c r="B46" s="83" t="s">
         <v>104</v>
       </c>
-      <c r="C46" s="72"/>
-      <c r="D46" s="72"/>
-      <c r="E46" s="72"/>
-      <c r="F46" s="72"/>
+      <c r="C46" s="83"/>
+      <c r="D46" s="83"/>
+      <c r="E46" s="83"/>
+      <c r="F46" s="83"/>
     </row>
     <row r="47" spans="1:7">
       <c r="C47" s="58" t="s">
@@ -5912,13 +5920,13 @@
       </c>
     </row>
     <row r="49" spans="1:7" ht="19">
-      <c r="B49" s="72" t="s">
+      <c r="B49" s="83" t="s">
         <v>108</v>
       </c>
-      <c r="C49" s="72"/>
-      <c r="D49" s="72"/>
-      <c r="E49" s="72"/>
-      <c r="F49" s="72"/>
+      <c r="C49" s="83"/>
+      <c r="D49" s="83"/>
+      <c r="E49" s="83"/>
+      <c r="F49" s="83"/>
     </row>
     <row r="50" spans="1:7">
       <c r="C50" s="58" t="s">
@@ -5946,23 +5954,23 @@
       </c>
     </row>
     <row r="52" spans="1:7" ht="27">
-      <c r="B52" s="73" t="s">
+      <c r="B52" s="85" t="s">
         <v>114</v>
       </c>
-      <c r="C52" s="73"/>
-      <c r="D52" s="73"/>
-      <c r="E52" s="73"/>
-      <c r="F52" s="73"/>
-      <c r="G52" s="73"/>
+      <c r="C52" s="85"/>
+      <c r="D52" s="85"/>
+      <c r="E52" s="85"/>
+      <c r="F52" s="85"/>
+      <c r="G52" s="85"/>
     </row>
     <row r="53" spans="1:7" ht="19">
-      <c r="B53" s="72" t="s">
+      <c r="B53" s="83" t="s">
         <v>115</v>
       </c>
-      <c r="C53" s="72"/>
-      <c r="D53" s="72"/>
-      <c r="E53" s="72"/>
-      <c r="F53" s="72"/>
+      <c r="C53" s="83"/>
+      <c r="D53" s="83"/>
+      <c r="E53" s="83"/>
+      <c r="F53" s="83"/>
     </row>
     <row r="54" spans="1:7">
       <c r="C54" s="58" t="s">
@@ -5973,7 +5981,7 @@
       </c>
     </row>
     <row r="55" spans="1:7">
-      <c r="A55" s="80" t="s">
+      <c r="A55" s="90" t="s">
         <v>279</v>
       </c>
       <c r="B55" s="5">
@@ -5990,7 +5998,7 @@
       </c>
     </row>
     <row r="56" spans="1:7">
-      <c r="A56" s="80"/>
+      <c r="A56" s="90"/>
       <c r="B56" s="5">
         <v>31</v>
       </c>
@@ -6005,7 +6013,7 @@
       </c>
     </row>
     <row r="57" spans="1:7">
-      <c r="A57" s="80"/>
+      <c r="A57" s="90"/>
       <c r="B57" s="5">
         <v>32</v>
       </c>
@@ -6020,7 +6028,7 @@
       </c>
     </row>
     <row r="58" spans="1:7">
-      <c r="A58" s="80"/>
+      <c r="A58" s="90"/>
       <c r="B58" s="5">
         <v>33</v>
       </c>
@@ -6035,7 +6043,7 @@
       </c>
     </row>
     <row r="59" spans="1:7">
-      <c r="A59" s="80"/>
+      <c r="A59" s="90"/>
       <c r="B59" s="5">
         <v>34</v>
       </c>
@@ -6047,13 +6055,13 @@
       </c>
     </row>
     <row r="60" spans="1:7" ht="19">
-      <c r="B60" s="72" t="s">
+      <c r="B60" s="83" t="s">
         <v>128</v>
       </c>
-      <c r="C60" s="72"/>
-      <c r="D60" s="72"/>
-      <c r="E60" s="72"/>
-      <c r="F60" s="72"/>
+      <c r="C60" s="83"/>
+      <c r="D60" s="83"/>
+      <c r="E60" s="83"/>
+      <c r="F60" s="83"/>
     </row>
     <row r="61" spans="1:7">
       <c r="C61" s="58" t="s">
@@ -6134,13 +6142,13 @@
       </c>
     </row>
     <row r="67" spans="1:7" ht="19">
-      <c r="B67" s="72" t="s">
+      <c r="B67" s="83" t="s">
         <v>142</v>
       </c>
-      <c r="C67" s="72"/>
-      <c r="D67" s="72"/>
-      <c r="E67" s="72"/>
-      <c r="F67" s="72"/>
+      <c r="C67" s="83"/>
+      <c r="D67" s="83"/>
+      <c r="E67" s="83"/>
+      <c r="F67" s="83"/>
     </row>
     <row r="68" spans="1:7">
       <c r="C68" s="58" t="s">
@@ -6204,13 +6212,13 @@
       </c>
     </row>
     <row r="73" spans="1:7" ht="19">
-      <c r="B73" s="72" t="s">
+      <c r="B73" s="83" t="s">
         <v>147</v>
       </c>
-      <c r="C73" s="72"/>
-      <c r="D73" s="72"/>
-      <c r="E73" s="72"/>
-      <c r="F73" s="72"/>
+      <c r="C73" s="83"/>
+      <c r="D73" s="83"/>
+      <c r="E73" s="83"/>
+      <c r="F73" s="83"/>
     </row>
     <row r="74" spans="1:7">
       <c r="C74" s="58" t="s">
@@ -6221,7 +6229,7 @@
       </c>
     </row>
     <row r="75" spans="1:7">
-      <c r="A75" s="81" t="s">
+      <c r="A75" s="91" t="s">
         <v>278</v>
       </c>
       <c r="B75" s="64">
@@ -6241,7 +6249,7 @@
       </c>
     </row>
     <row r="76" spans="1:7">
-      <c r="A76" s="82"/>
+      <c r="A76" s="92"/>
       <c r="B76" s="5">
         <v>45</v>
       </c>
@@ -6253,7 +6261,7 @@
       </c>
     </row>
     <row r="77" spans="1:7">
-      <c r="A77" s="82"/>
+      <c r="A77" s="92"/>
       <c r="B77" s="5">
         <v>46</v>
       </c>
@@ -6265,7 +6273,7 @@
       </c>
     </row>
     <row r="78" spans="1:7">
-      <c r="A78" s="82"/>
+      <c r="A78" s="92"/>
       <c r="B78" s="5">
         <v>47</v>
       </c>
@@ -6277,7 +6285,7 @@
       </c>
     </row>
     <row r="79" spans="1:7">
-      <c r="A79" s="83"/>
+      <c r="A79" s="93"/>
       <c r="B79" s="68">
         <v>48</v>
       </c>
@@ -6317,16 +6325,16 @@
       </c>
     </row>
     <row r="82" spans="1:6">
-      <c r="A82" s="84">
+      <c r="A82" s="71">
         <v>29</v>
       </c>
-      <c r="B82" s="85">
+      <c r="B82" s="72">
         <v>51</v>
       </c>
-      <c r="C82" s="86" t="s">
+      <c r="C82" s="73" t="s">
         <v>256</v>
       </c>
-      <c r="D82" s="87" t="s">
+      <c r="D82" s="74" t="s">
         <v>257</v>
       </c>
     </row>
@@ -6345,13 +6353,13 @@
       </c>
     </row>
     <row r="85" spans="1:6" ht="19">
-      <c r="B85" s="72" t="s">
+      <c r="B85" s="83" t="s">
         <v>160</v>
       </c>
-      <c r="C85" s="72"/>
-      <c r="D85" s="72"/>
-      <c r="E85" s="72"/>
-      <c r="F85" s="72"/>
+      <c r="C85" s="83"/>
+      <c r="D85" s="83"/>
+      <c r="E85" s="83"/>
+      <c r="F85" s="83"/>
     </row>
     <row r="86" spans="1:6">
       <c r="C86" s="58" t="s">
@@ -6379,13 +6387,13 @@
       </c>
     </row>
     <row r="88" spans="1:6" ht="19">
-      <c r="B88" s="72" t="s">
+      <c r="B88" s="83" t="s">
         <v>164</v>
       </c>
-      <c r="C88" s="72"/>
-      <c r="D88" s="72"/>
-      <c r="E88" s="72"/>
-      <c r="F88" s="72"/>
+      <c r="C88" s="83"/>
+      <c r="D88" s="83"/>
+      <c r="E88" s="83"/>
+      <c r="F88" s="83"/>
     </row>
     <row r="89" spans="1:6">
       <c r="C89" s="58" t="s">
@@ -6418,13 +6426,13 @@
       </c>
     </row>
     <row r="92" spans="1:6" ht="19">
-      <c r="B92" s="72" t="s">
+      <c r="B92" s="83" t="s">
         <v>171</v>
       </c>
-      <c r="C92" s="72"/>
-      <c r="D92" s="72"/>
-      <c r="E92" s="72"/>
-      <c r="F92" s="72"/>
+      <c r="C92" s="83"/>
+      <c r="D92" s="83"/>
+      <c r="E92" s="83"/>
+      <c r="F92" s="83"/>
     </row>
     <row r="93" spans="1:6">
       <c r="C93" s="58" t="s">
@@ -6505,13 +6513,13 @@
       </c>
     </row>
     <row r="99" spans="1:6" ht="19">
-      <c r="B99" s="72" t="s">
+      <c r="B99" s="83" t="s">
         <v>187</v>
       </c>
-      <c r="C99" s="72"/>
-      <c r="D99" s="72"/>
-      <c r="E99" s="72"/>
-      <c r="F99" s="72"/>
+      <c r="C99" s="83"/>
+      <c r="D99" s="83"/>
+      <c r="E99" s="83"/>
+      <c r="F99" s="83"/>
     </row>
     <row r="100" spans="1:6">
       <c r="C100" s="58" t="s">
@@ -6522,7 +6530,7 @@
       </c>
     </row>
     <row r="101" spans="1:6">
-      <c r="A101" s="80" t="s">
+      <c r="A101" s="90" t="s">
         <v>280</v>
       </c>
       <c r="B101" s="5">
@@ -6536,7 +6544,7 @@
       </c>
     </row>
     <row r="102" spans="1:6">
-      <c r="A102" s="80"/>
+      <c r="A102" s="90"/>
       <c r="B102" s="5">
         <v>60</v>
       </c>
@@ -6548,7 +6556,7 @@
       </c>
     </row>
     <row r="103" spans="1:6">
-      <c r="A103" s="80"/>
+      <c r="A103" s="90"/>
       <c r="B103" s="5">
         <v>61</v>
       </c>
@@ -6560,7 +6568,7 @@
       </c>
     </row>
     <row r="104" spans="1:6">
-      <c r="A104" s="80"/>
+      <c r="A104" s="90"/>
       <c r="B104" s="5">
         <v>62</v>
       </c>
@@ -6572,7 +6580,7 @@
       </c>
     </row>
     <row r="105" spans="1:6">
-      <c r="A105" s="80"/>
+      <c r="A105" s="90"/>
       <c r="B105" s="5">
         <v>63</v>
       </c>
@@ -6584,13 +6592,13 @@
       </c>
     </row>
     <row r="106" spans="1:6" ht="19">
-      <c r="B106" s="72" t="s">
+      <c r="B106" s="83" t="s">
         <v>198</v>
       </c>
-      <c r="C106" s="72"/>
-      <c r="D106" s="72"/>
-      <c r="E106" s="72"/>
-      <c r="F106" s="72"/>
+      <c r="C106" s="83"/>
+      <c r="D106" s="83"/>
+      <c r="E106" s="83"/>
+      <c r="F106" s="83"/>
     </row>
     <row r="107" spans="1:6">
       <c r="C107" s="58" t="s">
@@ -6601,7 +6609,7 @@
       </c>
     </row>
     <row r="108" spans="1:6">
-      <c r="A108" s="80" t="s">
+      <c r="A108" s="90" t="s">
         <v>281</v>
       </c>
       <c r="B108" s="5">
@@ -6615,7 +6623,7 @@
       </c>
     </row>
     <row r="109" spans="1:6">
-      <c r="A109" s="80"/>
+      <c r="A109" s="90"/>
       <c r="B109" s="5">
         <v>65</v>
       </c>
@@ -6627,7 +6635,7 @@
       </c>
     </row>
     <row r="110" spans="1:6">
-      <c r="A110" s="80"/>
+      <c r="A110" s="90"/>
       <c r="B110" s="5">
         <v>66</v>
       </c>
@@ -6639,7 +6647,7 @@
       </c>
     </row>
     <row r="111" spans="1:6">
-      <c r="A111" s="80"/>
+      <c r="A111" s="90"/>
       <c r="B111" s="5">
         <v>67</v>
       </c>
@@ -6654,7 +6662,7 @@
       </c>
     </row>
     <row r="112" spans="1:6">
-      <c r="A112" s="80"/>
+      <c r="A112" s="90"/>
       <c r="B112" s="5">
         <v>68</v>
       </c>
@@ -6666,7 +6674,7 @@
       </c>
     </row>
     <row r="113" spans="1:6">
-      <c r="A113" s="80"/>
+      <c r="A113" s="90"/>
       <c r="B113" s="5">
         <v>69</v>
       </c>
@@ -6681,13 +6689,13 @@
       </c>
     </row>
     <row r="114" spans="1:6" ht="19">
-      <c r="B114" s="72" t="s">
+      <c r="B114" s="83" t="s">
         <v>213</v>
       </c>
-      <c r="C114" s="72"/>
-      <c r="D114" s="72"/>
-      <c r="E114" s="72"/>
-      <c r="F114" s="72"/>
+      <c r="C114" s="83"/>
+      <c r="D114" s="83"/>
+      <c r="E114" s="83"/>
+      <c r="F114" s="83"/>
     </row>
     <row r="115" spans="1:6">
       <c r="C115" s="58" t="s">
@@ -6726,13 +6734,13 @@
       </c>
     </row>
     <row r="118" spans="1:6" ht="19">
-      <c r="B118" s="72" t="s">
+      <c r="B118" s="83" t="s">
         <v>224</v>
       </c>
-      <c r="C118" s="72"/>
-      <c r="D118" s="72"/>
-      <c r="E118" s="72"/>
-      <c r="F118" s="72"/>
+      <c r="C118" s="83"/>
+      <c r="D118" s="83"/>
+      <c r="E118" s="83"/>
+      <c r="F118" s="83"/>
     </row>
     <row r="119" spans="1:6">
       <c r="C119" s="58" t="s">
@@ -6743,7 +6751,7 @@
       </c>
     </row>
     <row r="120" spans="1:6">
-      <c r="A120" s="80" t="s">
+      <c r="A120" s="90" t="s">
         <v>282</v>
       </c>
       <c r="B120" s="5">
@@ -6757,7 +6765,7 @@
       </c>
     </row>
     <row r="121" spans="1:6">
-      <c r="A121" s="80"/>
+      <c r="A121" s="90"/>
       <c r="B121" s="5">
         <v>73</v>
       </c>
@@ -6769,7 +6777,7 @@
       </c>
     </row>
     <row r="122" spans="1:6">
-      <c r="A122" s="80"/>
+      <c r="A122" s="90"/>
       <c r="B122" s="5">
         <v>74</v>
       </c>
@@ -6781,7 +6789,7 @@
       </c>
     </row>
     <row r="123" spans="1:6">
-      <c r="A123" s="80"/>
+      <c r="A123" s="90"/>
       <c r="B123" s="5">
         <v>75</v>
       </c>
@@ -6793,13 +6801,13 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="19">
-      <c r="B124" s="72" t="s">
+      <c r="B124" s="83" t="s">
         <v>225</v>
       </c>
-      <c r="C124" s="72"/>
-      <c r="D124" s="72"/>
-      <c r="E124" s="72"/>
-      <c r="F124" s="72"/>
+      <c r="C124" s="83"/>
+      <c r="D124" s="83"/>
+      <c r="E124" s="83"/>
+      <c r="F124" s="83"/>
     </row>
     <row r="125" spans="1:6">
       <c r="C125" s="58" t="s">
@@ -6810,7 +6818,7 @@
       </c>
     </row>
     <row r="126" spans="1:6">
-      <c r="A126" s="79" t="s">
+      <c r="A126" s="89" t="s">
         <v>284</v>
       </c>
       <c r="B126" s="5">
@@ -6824,7 +6832,7 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="A127" s="79"/>
+      <c r="A127" s="89"/>
       <c r="B127" s="5">
         <v>77</v>
       </c>
@@ -6836,7 +6844,7 @@
       </c>
     </row>
     <row r="128" spans="1:6">
-      <c r="A128" s="79"/>
+      <c r="A128" s="89"/>
       <c r="B128" s="5">
         <v>78</v>
       </c>
@@ -6859,22 +6867,6 @@
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="B46:F46"/>
-    <mergeCell ref="C1:G1"/>
-    <mergeCell ref="C2:F2"/>
-    <mergeCell ref="B9:F9"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="B15:G15"/>
-    <mergeCell ref="B27:G27"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="B35:F35"/>
-    <mergeCell ref="B39:F39"/>
-    <mergeCell ref="B49:F49"/>
-    <mergeCell ref="B52:G52"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B60:F60"/>
-    <mergeCell ref="B67:F67"/>
     <mergeCell ref="A126:A128"/>
     <mergeCell ref="B118:F118"/>
     <mergeCell ref="B124:F124"/>
@@ -6890,6 +6882,22 @@
     <mergeCell ref="B106:F106"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B49:F49"/>
+    <mergeCell ref="B52:G52"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B60:F60"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B46:F46"/>
+    <mergeCell ref="C1:G1"/>
+    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="B9:F9"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="B15:G15"/>
+    <mergeCell ref="B27:G27"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="B35:F35"/>
+    <mergeCell ref="B39:F39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -6910,10 +6918,10 @@
       <c r="B1" s="4"/>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="92" t="s">
+      <c r="A3" s="94" t="s">
         <v>296</v>
       </c>
-      <c r="B3" s="92"/>
+      <c r="B3" s="94"/>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="58" t="s">
@@ -6922,7 +6930,7 @@
       <c r="B4" t="s">
         <v>117</v>
       </c>
-      <c r="C4" s="93" t="s">
+      <c r="C4" s="95" t="s">
         <v>296</v>
       </c>
     </row>
@@ -6933,16 +6941,16 @@
       <c r="B5" t="s">
         <v>119</v>
       </c>
-      <c r="C5" s="93"/>
+      <c r="C5" s="95"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="88" t="s">
+      <c r="A6" s="75" t="s">
         <v>120</v>
       </c>
-      <c r="B6" s="89" t="s">
+      <c r="B6" s="76" t="s">
         <v>121</v>
       </c>
-      <c r="C6" s="93"/>
+      <c r="C6" s="95"/>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="58" t="s">
@@ -6951,26 +6959,26 @@
       <c r="B7" t="s">
         <v>123</v>
       </c>
-      <c r="C7" s="93"/>
+      <c r="C7" s="95"/>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="90" t="s">
+      <c r="A8" s="75" t="s">
         <v>243</v>
       </c>
-      <c r="B8" s="91" t="s">
+      <c r="B8" s="76" t="s">
         <v>244</v>
       </c>
-      <c r="C8" s="93"/>
+      <c r="C8" s="95"/>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="92" t="s">
+      <c r="A10" s="94" t="s">
         <v>236</v>
       </c>
-      <c r="B10" s="92"/>
-      <c r="D10" s="92" t="s">
+      <c r="B10" s="94"/>
+      <c r="D10" s="94" t="s">
         <v>302</v>
       </c>
-      <c r="E10" s="92"/>
+      <c r="E10" s="94"/>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="58" t="s">
@@ -6979,10 +6987,10 @@
       <c r="B11" t="s">
         <v>293</v>
       </c>
-      <c r="C11" s="93" t="s">
+      <c r="C11" s="95" t="s">
         <v>236</v>
       </c>
-      <c r="D11" s="94" t="s">
+      <c r="D11" s="77" t="s">
         <v>239</v>
       </c>
     </row>
@@ -6993,8 +7001,8 @@
       <c r="B12" t="s">
         <v>294</v>
       </c>
-      <c r="C12" s="93"/>
-      <c r="D12" s="94" t="s">
+      <c r="C12" s="95"/>
+      <c r="D12" s="77" t="s">
         <v>290</v>
       </c>
     </row>
@@ -7005,40 +7013,40 @@
       <c r="B13" t="s">
         <v>295</v>
       </c>
-      <c r="C13" s="93"/>
-      <c r="D13" s="94" t="s">
+      <c r="C13" s="95"/>
+      <c r="D13" s="77" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="88" t="s">
+      <c r="A14" s="75" t="s">
         <v>120</v>
       </c>
-      <c r="B14" s="89" t="s">
+      <c r="B14" s="76" t="s">
         <v>121</v>
       </c>
-      <c r="C14" s="93"/>
-      <c r="D14" s="94" t="s">
+      <c r="C14" s="95"/>
+      <c r="D14" s="77" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="90" t="s">
+      <c r="A15" s="75" t="s">
         <v>243</v>
       </c>
-      <c r="B15" s="91" t="s">
+      <c r="B15" s="76" t="s">
         <v>244</v>
       </c>
-      <c r="C15" s="93"/>
-      <c r="D15" s="94" t="s">
+      <c r="C15" s="95"/>
+      <c r="D15" s="77" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="92" t="s">
+      <c r="A17" s="94" t="s">
         <v>297</v>
       </c>
-      <c r="B17" s="92"/>
+      <c r="B17" s="94"/>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
@@ -7049,10 +7057,10 @@
       </c>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="92" t="s">
+      <c r="A21" s="94" t="s">
         <v>236</v>
       </c>
-      <c r="B21" s="92"/>
+      <c r="B21" s="94"/>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
@@ -7071,10 +7079,10 @@
       </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="92" t="s">
+      <c r="A26" s="94" t="s">
         <v>302</v>
       </c>
-      <c r="B26" s="92"/>
+      <c r="B26" s="94"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -7097,117 +7105,160 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
     <row r="15" spans="1:6">
-      <c r="A15" s="95" t="s">
+      <c r="A15" s="100" t="s">
         <v>302</v>
       </c>
-      <c r="B15" s="96"/>
-      <c r="C15" s="101" t="s">
+      <c r="B15" s="101"/>
+      <c r="C15" s="100" t="s">
         <v>304</v>
       </c>
-      <c r="D15" s="102"/>
-      <c r="E15" s="109" t="s">
+      <c r="D15" s="101"/>
+      <c r="E15" s="102" t="s">
         <v>305</v>
       </c>
-      <c r="F15" s="110"/>
+      <c r="F15" s="103"/>
     </row>
     <row r="16" spans="1:6" ht="16" customHeight="1">
-      <c r="A16" s="97" t="s">
+      <c r="A16" s="78" t="s">
         <v>306</v>
       </c>
       <c r="B16" s="67" t="s">
         <v>116</v>
       </c>
-      <c r="C16" s="103" t="s">
+      <c r="C16" s="78" t="s">
         <v>307</v>
       </c>
-      <c r="D16" s="104" t="s">
+      <c r="D16" s="80" t="s">
         <v>116</v>
       </c>
-      <c r="E16" s="111" t="s">
+      <c r="E16" s="104" t="s">
         <v>116</v>
       </c>
-      <c r="F16" s="106"/>
+      <c r="F16" s="97"/>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" s="97" t="s">
+      <c r="A17" s="78" t="s">
         <v>308</v>
       </c>
       <c r="B17" s="67" t="s">
         <v>118</v>
       </c>
-      <c r="C17" s="103" t="s">
+      <c r="C17" s="78" t="s">
         <v>308</v>
       </c>
-      <c r="D17" s="104" t="s">
+      <c r="D17" s="80" t="s">
         <v>118</v>
       </c>
-      <c r="E17" s="105" t="s">
+      <c r="E17" s="96" t="s">
         <v>118</v>
       </c>
-      <c r="F17" s="106"/>
+      <c r="F17" s="97"/>
     </row>
     <row r="18" spans="1:6">
-      <c r="A18" s="100" t="s">
+      <c r="A18" s="96" t="s">
         <v>120</v>
       </c>
-      <c r="B18" s="99"/>
-      <c r="C18" s="105" t="s">
+      <c r="B18" s="97"/>
+      <c r="C18" s="96" t="s">
         <v>120</v>
       </c>
-      <c r="D18" s="106"/>
-      <c r="E18" s="105" t="s">
+      <c r="D18" s="97"/>
+      <c r="E18" s="96" t="s">
         <v>120</v>
       </c>
-      <c r="F18" s="106"/>
+      <c r="F18" s="97"/>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="97" t="s">
+      <c r="A19" s="78" t="s">
         <v>311</v>
       </c>
       <c r="B19" s="67" t="s">
         <v>309</v>
       </c>
-      <c r="C19" s="103" t="s">
+      <c r="C19" s="78" t="s">
         <v>309</v>
       </c>
-      <c r="D19" s="104" t="s">
+      <c r="D19" s="80" t="s">
         <v>122</v>
       </c>
-      <c r="E19" s="105" t="s">
+      <c r="E19" s="96" t="s">
         <v>122</v>
       </c>
-      <c r="F19" s="106"/>
+      <c r="F19" s="97"/>
     </row>
     <row r="20" spans="1:6">
-      <c r="A20" s="98" t="s">
+      <c r="A20" s="79" t="s">
         <v>310</v>
       </c>
       <c r="B20" s="70" t="s">
         <v>292</v>
       </c>
-      <c r="C20" s="107" t="s">
+      <c r="C20" s="98" t="s">
         <v>243</v>
       </c>
-      <c r="D20" s="108"/>
-      <c r="E20" s="107" t="s">
+      <c r="D20" s="99"/>
+      <c r="E20" s="98" t="s">
         <v>243</v>
       </c>
-      <c r="F20" s="108"/>
+      <c r="F20" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="E17:F17"/>
     <mergeCell ref="E19:F19"/>
     <mergeCell ref="E20:F20"/>
     <mergeCell ref="C18:D18"/>
     <mergeCell ref="C20:D20"/>
     <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="E17:F17"/>
     <mergeCell ref="E18:F18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1966C467-C770-CC4C-AF2D-8FBAAF09C3FF}">
+  <dimension ref="A3:C5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <cols>
+    <col min="1" max="1" width="12.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:3">
+      <c r="B3" t="s">
+        <v>314</v>
+      </c>
+      <c r="C3" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>312</v>
+      </c>
+      <c r="B4" t="s">
+        <v>316</v>
+      </c>
+      <c r="C4" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>313</v>
+      </c>
+      <c r="B5" t="s">
+        <v>318</v>
+      </c>
+      <c r="C5" t="s">
+        <v>319</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>